--- a/src/attributions/attributions_saliency_traj_208.xlsx
+++ b/src/attributions/attributions_saliency_traj_208.xlsx
@@ -999,5692 +999,5692 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.62428077601362e-05</v>
+        <v>0.0001231700152857229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.367604510160163e-05</v>
+        <v>0.0004158220253884792</v>
       </c>
       <c r="C2" t="n">
-        <v>4.041526699438691e-05</v>
+        <v>0.0001148688970715739</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001441335625713691</v>
+        <v>0.0002868770679924637</v>
       </c>
       <c r="E2" t="n">
-        <v>5.244758358458057e-05</v>
+        <v>7.265834574354813e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.665493856417015e-05</v>
+        <v>0.0002581146254669875</v>
       </c>
       <c r="G2" t="n">
-        <v>1.646208329475485e-05</v>
+        <v>6.216846668394282e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.493100512561796e-06</v>
+        <v>3.315204594400711e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>8.262411938630976e-06</v>
+        <v>1.004268233373296e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.770727976690978e-06</v>
+        <v>0.0002051219344139099</v>
       </c>
       <c r="K2" t="n">
-        <v>8.260270260507241e-05</v>
+        <v>0.0004348657093942165</v>
       </c>
       <c r="L2" t="n">
-        <v>1.616982808627654e-05</v>
+        <v>0.0001503536477684975</v>
       </c>
       <c r="M2" t="n">
-        <v>8.859715308062732e-05</v>
+        <v>0.0004306705086492002</v>
       </c>
       <c r="N2" t="n">
-        <v>1.721101580187678e-05</v>
+        <v>0.0001215618904097937</v>
       </c>
       <c r="O2" t="n">
-        <v>2.089080953737721e-05</v>
+        <v>0.000119736730994191</v>
       </c>
       <c r="P2" t="n">
-        <v>1.242289545189124e-05</v>
+        <v>8.883006375981495e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.546937321312726e-05</v>
+        <v>2.277632347613689e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>5.985018560750177e-06</v>
+        <v>6.464882608270273e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>9.949309060175437e-06</v>
+        <v>7.923319208202884e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>6.49788216833258e-06</v>
+        <v>8.464186248602346e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.766665602393914e-06</v>
+        <v>5.048796538176248e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.050460847793147e-05</v>
+        <v>4.588237061398104e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.193380740005523e-05</v>
+        <v>2.148159728676546e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.086552947526798e-05</v>
+        <v>0.0001451099233236164</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.094427898351569e-05</v>
+        <v>5.186578164284583e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.251378671440762e-05</v>
+        <v>6.070995084428432e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.399688805278856e-06</v>
+        <v>7.204474968602881e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.759864168590866e-06</v>
+        <v>1.606327532499563e-05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.120204953826033e-05</v>
+        <v>5.34979444637429e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.531348607386462e-05</v>
+        <v>4.909922427032143e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>5.019101809011772e-05</v>
+        <v>0.0001050780774676241</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.00830275187036e-05</v>
+        <v>9.050409062183462e-07</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.073126622941345e-05</v>
+        <v>8.603747119195759e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.321221811347641e-06</v>
+        <v>5.696448351955041e-05</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.725394425506238e-06</v>
+        <v>3.080686292378232e-05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.867826722445898e-05</v>
+        <v>1.135374623117968e-05</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.931888947292464e-07</v>
+        <v>4.582950350595638e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.839290391420946e-05</v>
+        <v>8.320141932927072e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.439508176001254e-06</v>
+        <v>6.79026561556384e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.041778316197451e-05</v>
+        <v>1.906555553432554e-05</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.110279481508769e-05</v>
+        <v>0.000111102664959617</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.557700645411387e-05</v>
+        <v>0.0001254680973943323</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.291523403779138e-07</v>
+        <v>2.858010338968597e-05</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.15436141641112e-05</v>
+        <v>3.138205283903517e-05</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.074615263671149e-06</v>
+        <v>4.890399395662826e-06</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.693483788287267e-06</v>
+        <v>1.99408477783436e-05</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.180628820904531e-06</v>
+        <v>0.0003058727015741169</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.423756748408778e-05</v>
+        <v>7.330341031774879e-05</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.682410745881498e-05</v>
+        <v>0.0001931741135194898</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.027794471359812e-05</v>
+        <v>3.671954254969023e-05</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.92618273710832e-05</v>
+        <v>2.494226100679953e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.233357236036682e-06</v>
+        <v>1.75791465153452e-05</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.378826659172773e-05</v>
+        <v>3.533649942255579e-05</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.987607892166125e-06</v>
+        <v>3.387717515579425e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.375136869493872e-06</v>
+        <v>2.649493762874044e-05</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.021170778083615e-05</v>
+        <v>7.615819049533457e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.59087204944808e-05</v>
+        <v>0.000113940637675114</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.20234612445347e-05</v>
+        <v>2.441956894472241e-07</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.693103695288301e-05</v>
+        <v>4.858287866227329e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.79819962795591e-05</v>
+        <v>0.000123995792819187</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.559652673677192e-06</v>
+        <v>9.179383050650358e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>4.436089511727914e-05</v>
+        <v>6.62305174046196e-05</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.693696145201102e-06</v>
+        <v>8.646613423479721e-05</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.460725252400152e-05</v>
+        <v>2.186887832067441e-05</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.197127054794692e-06</v>
+        <v>0.0001178389211418107</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.804010470455978e-06</v>
+        <v>8.607997006038204e-05</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.80183108872734e-06</v>
+        <v>2.47121715801768e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.986366992758121e-06</v>
+        <v>2.66260340140434e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.535633929161122e-06</v>
+        <v>1.325308585364837e-05</v>
       </c>
       <c r="BR2" t="n">
-        <v>6.693412160529988e-06</v>
+        <v>5.317487375577912e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.105071805795887e-05</v>
+        <v>2.52065910899546e-05</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.403586520609679e-05</v>
+        <v>1.867972059699241e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.643895979621448e-05</v>
+        <v>8.837490167934448e-05</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.146397335105576e-05</v>
+        <v>0.0002068329486064613</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.205521690892056e-06</v>
+        <v>5.08558923684177e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.512244388228282e-05</v>
+        <v>9.139241592492908e-05</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.631504675169708e-06</v>
+        <v>1.844558937591501e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.088514285489509e-07</v>
+        <v>0.000155155299580656</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.199636426463258e-05</v>
+        <v>2.895607758546248e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.952109025500249e-05</v>
+        <v>7.09144751454005e-06</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.268454752789694e-06</v>
+        <v>4.111306043341756e-05</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.917932079071761e-06</v>
+        <v>2.751675856416114e-05</v>
       </c>
       <c r="CE2" t="n">
-        <v>4.264887593308231e-06</v>
+        <v>0.0001106897834688425</v>
       </c>
       <c r="CF2" t="n">
-        <v>4.570769760903204e-06</v>
+        <v>7.103774987626821e-05</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.476025085547008e-05</v>
+        <v>8.165701001416892e-05</v>
       </c>
       <c r="CH2" t="n">
-        <v>2.152588058379479e-05</v>
+        <v>2.249803401355166e-06</v>
       </c>
       <c r="CI2" t="n">
-        <v>7.693131465202896e-07</v>
+        <v>2.370360562053975e-06</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.585101007454796e-06</v>
+        <v>6.112615210440708e-06</v>
       </c>
       <c r="CK2" t="n">
-        <v>4.635905042960076e-06</v>
+        <v>3.252789610996842e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.009857325901976e-06</v>
+        <v>9.742193469719496e-06</v>
       </c>
       <c r="CM2" t="n">
-        <v>9.868870620266534e-06</v>
+        <v>0.0001139651285484433</v>
       </c>
       <c r="CN2" t="n">
-        <v>5.040422911406495e-05</v>
+        <v>4.356370482128114e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>2.954179399239365e-05</v>
+        <v>7.458614709321409e-05</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.210755701526068e-05</v>
+        <v>0.0001729569921735674</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.839468495745678e-05</v>
+        <v>4.491579966270365e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.168327344203135e-05</v>
+        <v>3.867811301461188e-06</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.888989183702506e-05</v>
+        <v>2.464488352416083e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.870365395006957e-06</v>
+        <v>4.289017306291498e-05</v>
       </c>
       <c r="CU2" t="n">
-        <v>8.811643965600524e-07</v>
+        <v>8.568054909119383e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>3.263486178184394e-06</v>
+        <v>8.254250133177266e-06</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.106337913370226e-05</v>
+        <v>0.0001277867122553289</v>
       </c>
       <c r="CX2" t="n">
-        <v>6.868516720714979e-06</v>
+        <v>6.993242277530953e-05</v>
       </c>
       <c r="CY2" t="n">
-        <v>3.354521322762594e-05</v>
+        <v>9.845700697042048e-05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.086386302835308e-05</v>
+        <v>2.568473064457066e-05</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.406024125572003e-06</v>
+        <v>1.385386894980911e-05</v>
       </c>
       <c r="DB2" t="n">
-        <v>9.885128747555427e-06</v>
+        <v>1.111804340325762e-05</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.257725100207608e-06</v>
+        <v>3.078183726756833e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.711887075041886e-06</v>
+        <v>2.703787686186843e-06</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.643442919885274e-05</v>
+        <v>6.328315066639334e-05</v>
       </c>
       <c r="DF2" t="n">
-        <v>4.760914453072473e-05</v>
+        <v>0.000108256921521388</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.292115095769987e-05</v>
+        <v>3.733390622073784e-05</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.729278250830248e-05</v>
+        <v>8.345646347152069e-05</v>
       </c>
       <c r="DI2" t="n">
-        <v>5.404363400884904e-05</v>
+        <v>7.317384006455541e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.976031308004167e-05</v>
+        <v>8.73397511895746e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.950671321537811e-05</v>
+        <v>1.581202013767324e-07</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.945419171534013e-06</v>
+        <v>0.0001122430185205303</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.593768385850126e-06</v>
+        <v>1.489082933403552e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>3.120285327895544e-07</v>
+        <v>1.277682895306498e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.027546725003049e-05</v>
+        <v>7.489934796467423e-05</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.43762825045269e-06</v>
+        <v>4.544795592664741e-05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3.04629465972539e-05</v>
+        <v>5.831541784573346e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.780514452955686e-05</v>
+        <v>4.685840394813567e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>4.22555604018271e-06</v>
+        <v>0.0001021188727463596</v>
       </c>
       <c r="DT2" t="n">
-        <v>1.107448770198971e-05</v>
+        <v>2.748373117356095e-05</v>
       </c>
       <c r="DU2" t="n">
-        <v>1.76054127223324e-05</v>
+        <v>1.514989162387792e-05</v>
       </c>
       <c r="DV2" t="n">
-        <v>1.055424399964977e-05</v>
+        <v>0.0001203845822601579</v>
       </c>
       <c r="DW2" t="n">
-        <v>5.684729330823757e-06</v>
+        <v>4.476751200854778e-07</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.296178470511222e-05</v>
+        <v>1.022987089527305e-05</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.109043637370632e-06</v>
+        <v>1.403506121278042e-05</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.817011798266321e-05</v>
+        <v>3.474322875263169e-05</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.132011261186562e-05</v>
+        <v>6.840708374511451e-05</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.266548406420043e-05</v>
+        <v>4.173155321041122e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>3.424621809244854e-06</v>
+        <v>7.411190381390043e-07</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.554037953610532e-05</v>
+        <v>0.0001272600202355534</v>
       </c>
       <c r="EE2" t="n">
-        <v>1.179021091957111e-05</v>
+        <v>8.117842662613839e-05</v>
       </c>
       <c r="EF2" t="n">
-        <v>2.928616959252395e-05</v>
+        <v>1.392237754771486e-05</v>
       </c>
       <c r="EG2" t="n">
-        <v>8.303778486151714e-06</v>
+        <v>5.414319457486272e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>9.551297353027621e-07</v>
+        <v>3.515867138048634e-05</v>
       </c>
       <c r="EI2" t="n">
-        <v>1.785717540769838e-05</v>
+        <v>8.483009878546e-05</v>
       </c>
       <c r="EJ2" t="n">
-        <v>4.958898898621555e-06</v>
+        <v>2.433905683574267e-05</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.179447372123832e-05</v>
+        <v>4.869757322012447e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>3.813776856986806e-06</v>
+        <v>4.448775143828243e-07</v>
       </c>
       <c r="EM2" t="n">
-        <v>8.849856385495514e-06</v>
+        <v>3.381139322300442e-05</v>
       </c>
       <c r="EN2" t="n">
-        <v>1.563838304718956e-05</v>
+        <v>7.163453119574115e-07</v>
       </c>
       <c r="EO2" t="n">
-        <v>1.245462590304669e-05</v>
+        <v>5.326313839759678e-06</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.262033151760988e-06</v>
+        <v>9.496286656940356e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.385594441671856e-05</v>
+        <v>8.802308002486825e-05</v>
       </c>
       <c r="ER2" t="n">
-        <v>2.043878339463845e-06</v>
+        <v>4.217268724460155e-05</v>
       </c>
       <c r="ES2" t="n">
-        <v>1.911350409500301e-05</v>
+        <v>4.939360951539129e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>2.911599585786462e-05</v>
+        <v>0.0001068364799721166</v>
       </c>
       <c r="EU2" t="n">
-        <v>4.4749926928489e-06</v>
+        <v>6.531028338940814e-05</v>
       </c>
       <c r="EV2" t="n">
-        <v>2.359758946113288e-05</v>
+        <v>4.107716813450679e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>8.637814062240068e-06</v>
+        <v>7.871783600421622e-05</v>
       </c>
       <c r="EX2" t="n">
-        <v>8.735865776543505e-06</v>
+        <v>3.129550896119326e-05</v>
       </c>
       <c r="EY2" t="n">
-        <v>4.298121893953066e-07</v>
+        <v>0.0001288086059503257</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.094231083698105e-05</v>
+        <v>4.855325096286833e-05</v>
       </c>
       <c r="FA2" t="n">
-        <v>3.059845039388165e-05</v>
+        <v>0.0001047617333824746</v>
       </c>
       <c r="FB2" t="n">
-        <v>1.131535009335494e-05</v>
+        <v>1.61090720212087e-05</v>
       </c>
       <c r="FC2" t="n">
-        <v>7.692651706747711e-06</v>
+        <v>9.833522199187428e-06</v>
       </c>
       <c r="FD2" t="n">
-        <v>6.444812697736779e-06</v>
+        <v>6.004020178806968e-07</v>
       </c>
       <c r="FE2" t="n">
-        <v>6.072129053791286e-06</v>
+        <v>2.89424951915862e-05</v>
       </c>
       <c r="FF2" t="n">
-        <v>5.389414582168683e-06</v>
+        <v>1.901851192087634e-06</v>
       </c>
       <c r="FG2" t="n">
-        <v>3.612552973208949e-05</v>
+        <v>2.218515510321595e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>2.218149347754661e-06</v>
+        <v>0.0001106539712054655</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.033765784086427e-05</v>
+        <v>1.929844620462973e-05</v>
       </c>
       <c r="FJ2" t="n">
-        <v>1.382262507831911e-05</v>
+        <v>4.411577538121492e-05</v>
       </c>
       <c r="FK2" t="n">
-        <v>1.057952886185376e-05</v>
+        <v>9.380871779285371e-05</v>
       </c>
       <c r="FL2" t="n">
-        <v>9.471958037465811e-06</v>
+        <v>5.024980055168271e-05</v>
       </c>
       <c r="FM2" t="n">
-        <v>3.267565716669196e-06</v>
+        <v>4.549799632513896e-05</v>
       </c>
       <c r="FN2" t="n">
-        <v>2.078113175230101e-05</v>
+        <v>7.10757085471414e-05</v>
       </c>
       <c r="FO2" t="n">
-        <v>6.601576842513168e-06</v>
+        <v>1.250595869350946e-05</v>
       </c>
       <c r="FP2" t="n">
-        <v>1.59588689712109e-05</v>
+        <v>2.426531864330173e-05</v>
       </c>
       <c r="FQ2" t="n">
-        <v>3.232730159652419e-05</v>
+        <v>0.0001535292831249535</v>
       </c>
       <c r="FR2" t="n">
-        <v>1.59874907694757e-05</v>
+        <v>0.0002124831080436707</v>
       </c>
       <c r="FS2" t="n">
-        <v>1.815901850932278e-05</v>
+        <v>0.000377617048798129</v>
       </c>
       <c r="FT2" t="n">
-        <v>1.213963969348697e-05</v>
+        <v>4.030592663184507e-06</v>
       </c>
       <c r="FU2" t="n">
-        <v>1.725684455777809e-06</v>
+        <v>8.301667548948899e-05</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.182463392979116e-06</v>
+        <v>0.0001383418857585639</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.473891916248249e-05</v>
+        <v>6.270932499319315e-05</v>
       </c>
       <c r="FX2" t="n">
-        <v>6.663023668807e-06</v>
+        <v>3.98889860662166e-05</v>
       </c>
       <c r="FY2" t="n">
-        <v>1.372602127958089e-05</v>
+        <v>5.832727765664458e-05</v>
       </c>
       <c r="FZ2" t="n">
-        <v>2.795377440634184e-08</v>
+        <v>0.000137852955958806</v>
       </c>
       <c r="GA2" t="n">
-        <v>1.512354174337815e-05</v>
+        <v>8.877021900843829e-05</v>
       </c>
       <c r="GB2" t="n">
-        <v>4.147114395891549e-06</v>
+        <v>5.907807644689456e-05</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.328935028752312e-05</v>
+        <v>9.142039198195562e-05</v>
       </c>
       <c r="GD2" t="n">
-        <v>1.313398024649359e-05</v>
+        <v>0.0001174905846710317</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.720293196034618e-05</v>
+        <v>0.0001248769694939256</v>
       </c>
       <c r="GF2" t="n">
-        <v>2.443429548293352e-05</v>
+        <v>7.137794455047697e-05</v>
       </c>
       <c r="GG2" t="n">
-        <v>1.299766427109716e-05</v>
+        <v>4.085457840119489e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.896054145968719e-09</v>
+        <v>2.355789119334872e-09</v>
       </c>
       <c r="B3" t="n">
-        <v>1.459439680218111e-08</v>
+        <v>6.750382475217975e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.197475729686204e-10</v>
+        <v>1.767699653321131e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.587112130607693e-08</v>
+        <v>2.177822366888904e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.163976997593409e-09</v>
+        <v>1.38665773308233e-10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.791998660571892e-09</v>
+        <v>5.313741446855147e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>2.059929782305403e-09</v>
+        <v>1.213541211964042e-10</v>
       </c>
       <c r="H3" t="n">
-        <v>4.418005516981793e-09</v>
+        <v>2.776400886972397e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>3.727168573774975e-11</v>
+        <v>1.645346081602383e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.693319954895969e-09</v>
+        <v>7.250436362404855e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.024577844788155e-08</v>
+        <v>6.946193842338744e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.423856449411787e-10</v>
+        <v>2.287606770678963e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>8.607434764940081e-09</v>
+        <v>6.111280370646455e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>5.024194393854486e-09</v>
+        <v>4.070130898981006e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>9.520033650289861e-09</v>
+        <v>5.157828830704148e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>5.174692674358994e-09</v>
+        <v>4.508509399148153e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.992153966933756e-09</v>
+        <v>1.381802783306796e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>8.785094873786647e-11</v>
+        <v>1.890609890864425e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.924543857612093e-11</v>
+        <v>1.600567456350177e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.062191472087306e-09</v>
+        <v>5.729761110018217e-10</v>
       </c>
       <c r="U3" t="n">
-        <v>1.430887852649221e-09</v>
+        <v>1.750745992623592e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.17535608918007e-10</v>
+        <v>2.90034440908471e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>6.457308465712686e-09</v>
+        <v>9.923853960813744e-10</v>
       </c>
       <c r="X3" t="n">
-        <v>3.679354154684233e-09</v>
+        <v>1.280158423710986e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.791715468854818e-09</v>
+        <v>1.7665485740892e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.214521787115899e-10</v>
+        <v>1.373250180236596e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.047324170779575e-09</v>
+        <v>9.969186587355239e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.880162857683445e-10</v>
+        <v>2.894109396578415e-10</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.763515303376266e-10</v>
+        <v>1.726174980731798e-09</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.051784659367172e-09</v>
+        <v>7.862016038195918e-10</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.289303552809429e-09</v>
+        <v>1.637198820958474e-09</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.187107384088449e-09</v>
+        <v>4.526791719250411e-10</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.853280640062849e-09</v>
+        <v>3.900803680068066e-09</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.810132706178365e-10</v>
+        <v>1.162913543240052e-09</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.408289206419113e-09</v>
+        <v>5.499127375685475e-09</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.747009865890277e-10</v>
+        <v>2.788790309793399e-10</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.237051820510374e-10</v>
+        <v>1.634388624438543e-09</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.996874970406793e-09</v>
+        <v>6.61440568983096e-10</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.503712875385645e-10</v>
+        <v>2.952702304881427e-09</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.977234154182383e-09</v>
+        <v>1.543543071136355e-09</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.506891833535917e-09</v>
+        <v>1.030988627803708e-09</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.312533859376686e-09</v>
+        <v>1.861152010285139e-09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.264137544116807e-09</v>
+        <v>3.948420201904668e-10</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.02896130399688e-09</v>
+        <v>1.100862623282239e-09</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.274175514571652e-09</v>
+        <v>6.435569299689803e-10</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.98063973502849e-09</v>
+        <v>2.222463546530662e-09</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.556949898126277e-09</v>
+        <v>5.951487302979785e-09</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.163056539965623e-09</v>
+        <v>4.664098440798625e-09</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.914957578236681e-09</v>
+        <v>1.98008831553409e-10</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.867330595179851e-09</v>
+        <v>6.883960956827195e-09</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.470896820483404e-10</v>
+        <v>6.333219726428752e-09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.264520375192205e-09</v>
+        <v>1.181429509777843e-09</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.499678464218391e-09</v>
+        <v>5.310919481971155e-10</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.809668053771475e-09</v>
+        <v>5.904866040573609e-10</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.546233973139579e-09</v>
+        <v>1.703703178534965e-09</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.515755242489149e-09</v>
+        <v>4.141334775109584e-10</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.603742859681347e-09</v>
+        <v>2.602162929576934e-11</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.946077077263908e-09</v>
+        <v>3.717507635059292e-09</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.787123420944226e-09</v>
+        <v>4.252516117020377e-09</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.875736537788498e-09</v>
+        <v>2.036235624558458e-09</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.340864835304046e-09</v>
+        <v>1.245956338102872e-09</v>
       </c>
       <c r="BJ3" t="n">
-        <v>7.611878238833469e-09</v>
+        <v>2.81907075461163e-09</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.265297644437169e-09</v>
+        <v>9.17680487155792e-10</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.966689782724075e-09</v>
+        <v>1.106224001290457e-09</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.059757253647376e-09</v>
+        <v>1.736294219512047e-09</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.11784575934837e-09</v>
+        <v>6.028327836915537e-11</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.291095785838081e-09</v>
+        <v>1.544712691092798e-10</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.533821510032681e-10</v>
+        <v>1.447943764887327e-09</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.524276426247752e-10</v>
+        <v>6.303057520362643e-10</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.866883092560556e-09</v>
+        <v>8.980922117096668e-10</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.167405144248846e-11</v>
+        <v>1.664770432618923e-09</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.929384288589802e-10</v>
+        <v>1.363698182155204e-10</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.082279266206854e-10</v>
+        <v>1.317363218511503e-09</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.788518553373478e-09</v>
+        <v>3.239083667949672e-09</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.599802401663908e-09</v>
+        <v>1.929371329367768e-09</v>
       </c>
       <c r="BX3" t="n">
-        <v>2.334460402764194e-09</v>
+        <v>3.903312950637172e-10</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.489951660995416e-10</v>
+        <v>1.917133785056535e-09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.378180902733561e-09</v>
+        <v>3.039451579311958e-09</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.02025315868093e-09</v>
+        <v>2.24015161975899e-09</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.5913035333881e-09</v>
+        <v>6.130655427760701e-10</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.520837760755512e-09</v>
+        <v>4.450624868646003e-10</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.19830084427997e-10</v>
+        <v>6.207035441185837e-10</v>
       </c>
       <c r="CE3" t="n">
-        <v>2.148068611873555e-09</v>
+        <v>2.800919940426638e-09</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.356635331324242e-09</v>
+        <v>1.403045735148822e-10</v>
       </c>
       <c r="CG3" t="n">
-        <v>8.415320107424407e-10</v>
+        <v>1.070158850424718e-09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.119218717704484e-09</v>
+        <v>2.277708854858673e-10</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.093202861568443e-09</v>
+        <v>1.068989008423671e-09</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.916364289478167e-11</v>
+        <v>5.741385700197554e-10</v>
       </c>
       <c r="CK3" t="n">
-        <v>4.200872982806914e-11</v>
+        <v>4.80317119411211e-10</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.304701762767536e-09</v>
+        <v>3.516476554388248e-10</v>
       </c>
       <c r="CM3" t="n">
-        <v>4.110600748674642e-10</v>
+        <v>6.885247927357341e-11</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.68595704064245e-09</v>
+        <v>3.959055305813308e-09</v>
       </c>
       <c r="CO3" t="n">
-        <v>5.534739333512562e-11</v>
+        <v>4.215605642343689e-09</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.544628285860995e-09</v>
+        <v>5.293791627281053e-09</v>
       </c>
       <c r="CQ3" t="n">
-        <v>8.437889831292011e-10</v>
+        <v>9.80231340541593e-10</v>
       </c>
       <c r="CR3" t="n">
-        <v>3.327563335986383e-09</v>
+        <v>6.866003321448488e-10</v>
       </c>
       <c r="CS3" t="n">
-        <v>4.398926112259005e-09</v>
+        <v>2.218626497796361e-11</v>
       </c>
       <c r="CT3" t="n">
-        <v>4.757644056496702e-09</v>
+        <v>1.928875725809576e-09</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.678045369324366e-09</v>
+        <v>1.114043968186706e-09</v>
       </c>
       <c r="CV3" t="n">
-        <v>8.350635738452183e-10</v>
+        <v>1.20402954273402e-09</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.603851051967808e-09</v>
+        <v>2.749274141677915e-09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.905470226049033e-09</v>
+        <v>6.097268245852661e-10</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.725110359591554e-09</v>
+        <v>1.68055902527442e-09</v>
       </c>
       <c r="CZ3" t="n">
-        <v>9.753119423194789e-10</v>
+        <v>6.878262959197912e-10</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.526717086086649e-09</v>
+        <v>1.443193231587259e-09</v>
       </c>
       <c r="DB3" t="n">
-        <v>9.006731471750129e-11</v>
+        <v>6.361997040293943e-10</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.694255651913835e-10</v>
+        <v>2.009011290660112e-10</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.556664241952888e-09</v>
+        <v>1.188690118558711e-10</v>
       </c>
       <c r="DE3" t="n">
-        <v>3.870503917369206e-11</v>
+        <v>2.149511679760963e-10</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.422370554671204e-10</v>
+        <v>1.140700423007956e-09</v>
       </c>
       <c r="DG3" t="n">
-        <v>8.476629176357164e-09</v>
+        <v>3.104897450256772e-10</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.621876677404543e-08</v>
+        <v>4.712549239727082e-10</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.301452012825166e-08</v>
+        <v>2.018751971144539e-10</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.581516584359122e-09</v>
+        <v>3.767099965301668e-09</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.804223075969503e-09</v>
+        <v>1.880872346760043e-09</v>
       </c>
       <c r="DL3" t="n">
-        <v>1.018984008283041e-08</v>
+        <v>3.974091278280412e-09</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.102075319892037e-09</v>
+        <v>1.318099740466039e-09</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.151723657727871e-10</v>
+        <v>1.206580280133096e-09</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.340537902905226e-09</v>
+        <v>3.749547339282344e-10</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.52140708312254e-09</v>
+        <v>8.779856841556466e-10</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.665593218902472e-10</v>
+        <v>2.352424643969897e-10</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.139568217567444e-09</v>
+        <v>1.922560721734357e-10</v>
       </c>
       <c r="DS3" t="n">
-        <v>2.186975933682334e-09</v>
+        <v>1.06125691567982e-10</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.87671944651413e-09</v>
+        <v>1.161351459444404e-09</v>
       </c>
       <c r="DU3" t="n">
-        <v>8.087984726401487e-10</v>
+        <v>3.260450132103188e-09</v>
       </c>
       <c r="DV3" t="n">
-        <v>5.975173245076348e-09</v>
+        <v>4.804695530324921e-10</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.992136233752717e-09</v>
+        <v>8.246080485108109e-10</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.260965719675823e-09</v>
+        <v>6.056111861996172e-11</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.122830965513913e-09</v>
+        <v>1.665093285474484e-09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.293362972276668e-09</v>
+        <v>1.143006911341615e-09</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.407493011029715e-09</v>
+        <v>9.349926388679819e-10</v>
       </c>
       <c r="EB3" t="n">
-        <v>4.999319624943155e-09</v>
+        <v>8.961482111935481e-10</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.887662248734046e-09</v>
+        <v>3.031946915754702e-10</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.660100723555047e-09</v>
+        <v>3.321971142611346e-09</v>
       </c>
       <c r="EE3" t="n">
-        <v>5.07263786531098e-10</v>
+        <v>2.36229746874983e-09</v>
       </c>
       <c r="EF3" t="n">
-        <v>6.858028589462606e-10</v>
+        <v>1.25792720684359e-09</v>
       </c>
       <c r="EG3" t="n">
-        <v>4.005134557338863e-10</v>
+        <v>1.164463636627033e-09</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.428149153439364e-10</v>
+        <v>1.325682674746531e-09</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.048233722045211e-09</v>
+        <v>1.814519645648716e-09</v>
       </c>
       <c r="EJ3" t="n">
-        <v>2.111624430867209e-09</v>
+        <v>5.382001788678537e-11</v>
       </c>
       <c r="EK3" t="n">
-        <v>1.807729521630108e-09</v>
+        <v>7.298593396320996e-10</v>
       </c>
       <c r="EL3" t="n">
-        <v>4.161972433358585e-10</v>
+        <v>1.084531797701516e-09</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.518688952373282e-09</v>
+        <v>5.984777673440078e-10</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.02633324061685e-09</v>
+        <v>2.989115621687688e-10</v>
       </c>
       <c r="EO3" t="n">
-        <v>3.728476971609496e-10</v>
+        <v>1.841654329037823e-10</v>
       </c>
       <c r="EP3" t="n">
-        <v>3.21237980660527e-10</v>
+        <v>1.833671214868104e-09</v>
       </c>
       <c r="EQ3" t="n">
-        <v>2.977847524121557e-09</v>
+        <v>1.213622535800596e-10</v>
       </c>
       <c r="ER3" t="n">
-        <v>4.357099125940067e-10</v>
+        <v>1.417789496915844e-10</v>
       </c>
       <c r="ES3" t="n">
-        <v>2.974014812195946e-09</v>
+        <v>6.888031256480076e-10</v>
       </c>
       <c r="ET3" t="n">
-        <v>6.785720874091794e-10</v>
+        <v>9.724999694427083e-10</v>
       </c>
       <c r="EU3" t="n">
-        <v>1.842989094669178e-10</v>
+        <v>3.165126216675418e-10</v>
       </c>
       <c r="EV3" t="n">
-        <v>5.496783916925096e-09</v>
+        <v>9.042310233908779e-10</v>
       </c>
       <c r="EW3" t="n">
-        <v>1.158752982455269e-09</v>
+        <v>1.744108857337778e-09</v>
       </c>
       <c r="EX3" t="n">
-        <v>7.357136011520993e-10</v>
+        <v>6.427957610632973e-10</v>
       </c>
       <c r="EY3" t="n">
-        <v>1.643030933529133e-09</v>
+        <v>3.166444439983707e-09</v>
       </c>
       <c r="EZ3" t="n">
-        <v>2.060846160389929e-09</v>
+        <v>5.217891674291764e-10</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.898610380024479e-09</v>
+        <v>1.91534321736242e-09</v>
       </c>
       <c r="FB3" t="n">
-        <v>5.288127158387113e-10</v>
+        <v>7.572709126435484e-11</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.581522246496547e-09</v>
+        <v>7.950779479237724e-10</v>
       </c>
       <c r="FD3" t="n">
-        <v>3.499270040396851e-10</v>
+        <v>4.131265884943502e-10</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.055718013009965e-10</v>
+        <v>5.132856917278161e-10</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.091162798478763e-09</v>
+        <v>5.416652681944356e-10</v>
       </c>
       <c r="FG3" t="n">
-        <v>2.409973554051703e-09</v>
+        <v>6.284554820989996e-11</v>
       </c>
       <c r="FH3" t="n">
-        <v>6.34541919009024e-10</v>
+        <v>3.386637192903663e-09</v>
       </c>
       <c r="FI3" t="n">
-        <v>4.284843146962203e-09</v>
+        <v>1.842856978129248e-10</v>
       </c>
       <c r="FJ3" t="n">
-        <v>2.783995034505438e-09</v>
+        <v>1.726721432504519e-09</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.234266688854291e-09</v>
+        <v>3.820240512819595e-10</v>
       </c>
       <c r="FL3" t="n">
-        <v>6.686076692297149e-10</v>
+        <v>7.595321038778025e-10</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.803594051885682e-09</v>
+        <v>5.580276796202099e-10</v>
       </c>
       <c r="FN3" t="n">
-        <v>5.005383663103657e-09</v>
+        <v>1.675363292541476e-09</v>
       </c>
       <c r="FO3" t="n">
-        <v>2.01080152528732e-10</v>
+        <v>3.861446717934314e-09</v>
       </c>
       <c r="FP3" t="n">
-        <v>1.975713592727857e-09</v>
+        <v>4.302839196057562e-10</v>
       </c>
       <c r="FQ3" t="n">
-        <v>1.590939491258325e-09</v>
+        <v>5.525200297284982e-09</v>
       </c>
       <c r="FR3" t="n">
-        <v>2.106686158853677e-09</v>
+        <v>1.876375055331891e-09</v>
       </c>
       <c r="FS3" t="n">
-        <v>2.278943700417813e-10</v>
+        <v>4.68108662943223e-10</v>
       </c>
       <c r="FT3" t="n">
-        <v>1.050838882576954e-08</v>
+        <v>4.938741859916718e-09</v>
       </c>
       <c r="FU3" t="n">
-        <v>1.990124065542886e-09</v>
+        <v>2.216853811631836e-09</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.62555591209923e-09</v>
+        <v>1.194631282785963e-09</v>
       </c>
       <c r="FW3" t="n">
-        <v>9.237753340052279e-10</v>
+        <v>3.384205360390524e-09</v>
       </c>
       <c r="FX3" t="n">
-        <v>4.154659949406891e-10</v>
+        <v>9.001272505138047e-10</v>
       </c>
       <c r="FY3" t="n">
-        <v>3.271381388003647e-09</v>
+        <v>5.640393152539502e-10</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.400771720838634e-09</v>
+        <v>8.572647036686476e-10</v>
       </c>
       <c r="GA3" t="n">
-        <v>1.354030776390402e-09</v>
+        <v>3.37986394427503e-09</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.119210502054102e-09</v>
+        <v>2.112149899424764e-10</v>
       </c>
       <c r="GC3" t="n">
-        <v>5.036864703100719e-09</v>
+        <v>3.303402218435281e-09</v>
       </c>
       <c r="GD3" t="n">
-        <v>3.861441832953005e-09</v>
+        <v>3.659766045771562e-09</v>
       </c>
       <c r="GE3" t="n">
-        <v>4.683179177789043e-09</v>
+        <v>6.401146279699788e-10</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.513093983440683e-09</v>
+        <v>5.115947665501608e-10</v>
       </c>
       <c r="GG3" t="n">
-        <v>2.827568179597506e-09</v>
+        <v>6.831837318088674e-10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0007338452851399779</v>
+        <v>1.072411777158777e-07</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01048913132399321</v>
+        <v>1.345173586742021e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005411871825344861</v>
+        <v>5.528107180907682e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003356848144903779</v>
+        <v>6.197507786964707e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005043690907768905</v>
+        <v>4.406226992159645e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006228816695511341</v>
+        <v>2.406700559731689e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006960373721085489</v>
+        <v>3.778616814997804e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002518243622034788</v>
+        <v>4.053788984492712e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006808149628341198</v>
+        <v>1.323360692140341e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001394853927195072</v>
+        <v>2.030475059200398e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009572334587574005</v>
+        <v>1.471654854867666e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000130572821944952</v>
+        <v>7.632965548509674e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002936752280220389</v>
+        <v>8.827234978525667e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007181367836892605</v>
+        <v>5.224922006163979e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005338997580111027</v>
+        <v>2.767449586826842e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001215740048792213</v>
+        <v>3.873696243772429e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000534411461558193</v>
+        <v>1.659108761487005e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0006207319675013423</v>
+        <v>1.289301678752963e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.375629264861345e-06</v>
+        <v>3.277749272001529e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007976730703376234</v>
+        <v>5.681762615949992e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004212465137243271</v>
+        <v>1.949019718949785e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009325339924544096</v>
+        <v>5.822315074510698e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001295336638577282</v>
+        <v>4.171511136519257e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.433260280871764e-05</v>
+        <v>5.038826884629088e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003942583280149847</v>
+        <v>2.023595868649863e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001297747250646353</v>
+        <v>2.766902014172956e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007686633616685867</v>
+        <v>1.844656907223907e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.684377927333117e-06</v>
+        <v>3.585809622563829e-07</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.994449358899146e-05</v>
+        <v>8.593295319769823e-08</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005090241902507842</v>
+        <v>4.588602280364285e-07</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0002160069416277111</v>
+        <v>4.321884716773639e-07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.087565371766686e-05</v>
+        <v>2.760144184321689e-07</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.000509515986777842</v>
+        <v>2.585150014056126e-07</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0002138765121344477</v>
+        <v>1.796243793705798e-07</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.322463691001758e-05</v>
+        <v>9.338926361124322e-07</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0002598126884549856</v>
+        <v>1.106054412502999e-07</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.001051180181093514</v>
+        <v>4.0413300439468e-07</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0006823823205195367</v>
+        <v>3.11033488742396e-07</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0001607257727300748</v>
+        <v>2.645953145474778e-07</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0003967210650444031</v>
+        <v>4.029310503028682e-07</v>
       </c>
       <c r="AO4" t="n">
-        <v>3.208529960829765e-05</v>
+        <v>8.458626155061211e-08</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001451033516786993</v>
+        <v>2.542710717534646e-07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.698897388763726e-05</v>
+        <v>4.5562451589376e-08</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0008208724902942777</v>
+        <v>3.545588072029204e-07</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0008966730674728751</v>
+        <v>2.280203119653379e-07</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0001985157432500273</v>
+        <v>1.216602356635121e-07</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005680604372173548</v>
+        <v>1.53271435010538e-06</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0005944832228124142</v>
+        <v>6.42467682610004e-07</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0006192162982188165</v>
+        <v>3.08301821405621e-07</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004672636860050261</v>
+        <v>2.884309253659012e-07</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002942148596048355</v>
+        <v>1.354466348857386e-06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00127155939117074</v>
+        <v>1.696127682748738e-09</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.000899986713193357</v>
+        <v>9.323575511643867e-08</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001369021949358284</v>
+        <v>3.349450850009816e-08</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004062036750838161</v>
+        <v>9.997904726333218e-08</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.002391849411651492</v>
+        <v>2.538094179271866e-07</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002024014247581363</v>
+        <v>2.213991479038668e-07</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0001535785122541711</v>
+        <v>5.514880285772961e-08</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0008650775998830795</v>
+        <v>6.211137133504963e-07</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001388612436130643</v>
+        <v>1.420306148247619e-07</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00014170550275594</v>
+        <v>3.814710112237663e-07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0008677627192810178</v>
+        <v>4.117334242437209e-07</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0007897790055721998</v>
+        <v>8.335163670381007e-09</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004290463984943926</v>
+        <v>3.508553447773011e-09</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001581182470545173</v>
+        <v>5.293510980663996e-07</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0009819932747632265</v>
+        <v>1.467969124036017e-08</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0001067221164703369</v>
+        <v>3.194164150954748e-07</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0006758893723599613</v>
+        <v>2.27511947059611e-07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003003107849508524</v>
+        <v>2.983242382015305e-07</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.000604920089245e-06</v>
+        <v>1.743101165629923e-07</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0004180485266260803</v>
+        <v>1.678880465760813e-07</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0001913707092171535</v>
+        <v>2.500928815152292e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0003286992141511291</v>
+        <v>1.452174132055006e-07</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003749952185899019</v>
+        <v>7.506828296754975e-07</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0005208238144405186</v>
+        <v>2.055253673916013e-07</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0006045022746548057</v>
+        <v>4.472407795219624e-07</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0001275303220609203</v>
+        <v>1.979909995952767e-07</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0009015799732878804</v>
+        <v>1.118624027185433e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001092350139515474</v>
+        <v>3.639595718141209e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0001929778372868896</v>
+        <v>9.780777787682382e-08</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0009246154222637415</v>
+        <v>8.7349619093402e-08</v>
       </c>
       <c r="CD4" t="n">
-        <v>7.072027074173093e-05</v>
+        <v>1.193181375924723e-08</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001779189915396273</v>
+        <v>4.648424578590493e-07</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0007452475256286561</v>
+        <v>1.048384064006314e-07</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0004176476795691997</v>
+        <v>9.990672822368651e-08</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0005375428590923548</v>
+        <v>5.64565851846055e-08</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0008704829961061478</v>
+        <v>5.552922743845556e-07</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0005817210767418146</v>
+        <v>1.530822046902358e-08</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0003779544786084443</v>
+        <v>1.151354496187196e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.000652638147585094</v>
+        <v>4.309855938799956e-08</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001770539092831314</v>
+        <v>2.280398945231354e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0007892001303844154</v>
+        <v>4.900845169686363e-07</v>
       </c>
       <c r="CO4" t="n">
-        <v>7.104999531293288e-05</v>
+        <v>5.031506589148194e-07</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001711860415525734</v>
+        <v>1.522381722907085e-07</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0006912231910973787</v>
+        <v>2.274881580888177e-07</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001967445481568575</v>
+        <v>8.590323830048874e-08</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001688399934209883</v>
+        <v>4.842027010454331e-07</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001671532983891666</v>
+        <v>4.864981519858702e-07</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002284733927808702</v>
+        <v>2.10465884720179e-07</v>
       </c>
       <c r="CV4" t="n">
-        <v>5.095858796266839e-05</v>
+        <v>1.22872862107215e-07</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.00175011286046356</v>
+        <v>4.409352243328613e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0008686938090249896</v>
+        <v>1.841090693233127e-07</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0008444323902949691</v>
+        <v>1.648615750582394e-07</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0004313512763474137</v>
+        <v>1.404994520726177e-08</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0009925022022798657</v>
+        <v>6.002511554470402e-07</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0005205720663070679</v>
+        <v>2.315145053444212e-08</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.000935383839532733</v>
+        <v>1.266198808025365e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004381677426863462</v>
+        <v>7.463312812205913e-08</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.000436769041698426</v>
+        <v>8.059896572376601e-08</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.002577622886747122</v>
+        <v>8.049203188420506e-07</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0002645254717208445</v>
+        <v>2.676012229585467e-07</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002288786927238107</v>
+        <v>1.979280739305977e-07</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002111626090481877</v>
+        <v>1.015505759482949e-07</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0007690577767789364</v>
+        <v>2.652217006016144e-07</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0006380504346452653</v>
+        <v>3.659047820292471e-08</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.001270423759706318</v>
+        <v>7.174581355684495e-07</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001490099471993744</v>
+        <v>3.962281311942206e-07</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0004431871930137277</v>
+        <v>1.827447846380892e-07</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0009969430975615978</v>
+        <v>5.686209192390379e-07</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.000612617121078074</v>
+        <v>1.449306523682026e-07</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003241153026465327</v>
+        <v>3.75531612917257e-07</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003796533273998648</v>
+        <v>1.94994555613448e-07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0004875555168837309</v>
+        <v>6.605806674997439e-07</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0003522367915138602</v>
+        <v>2.262894014393169e-07</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0002742399228736758</v>
+        <v>5.261505293674418e-07</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0003712562611326575</v>
+        <v>1.142597838565962e-07</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.201953273266554e-05</v>
+        <v>1.356329164536874e-07</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000996829941868782</v>
+        <v>2.172181723381073e-08</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0004500251961871982</v>
+        <v>7.521001634813729e-07</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003112179692834616</v>
+        <v>6.20313613808321e-08</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0007562802638858557</v>
+        <v>2.821210784986761e-07</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0007014321745373309</v>
+        <v>2.301067070220597e-07</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0003989287652075291</v>
+        <v>9.305962578309845e-08</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0001468806876800954</v>
+        <v>2.6106741302101e-07</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.001315886620432138</v>
+        <v>5.880129947399837e-07</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0008704073843546212</v>
+        <v>7.130292090096191e-08</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001508332206867635</v>
+        <v>1.017969211147829e-07</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.001046181074343622</v>
+        <v>1.957133122232335e-08</v>
       </c>
       <c r="EI4" t="n">
-        <v>3.442545130383223e-05</v>
+        <v>8.175469190518925e-08</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0003140458720736206</v>
+        <v>2.068463800242171e-07</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0003567980311345309</v>
+        <v>2.259809690485781e-07</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0004178680828772485</v>
+        <v>4.893074390110996e-09</v>
       </c>
       <c r="EM4" t="n">
-        <v>3.282515535829589e-06</v>
+        <v>5.014850312790031e-09</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0003301895631011575</v>
+        <v>2.39989844885713e-07</v>
       </c>
       <c r="EO4" t="n">
-        <v>5.417643114924431e-05</v>
+        <v>1.898674995004512e-08</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001180062768980861</v>
+        <v>2.301886325994928e-07</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0004855045990552753</v>
+        <v>2.559413019298518e-07</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0007663443684577942</v>
+        <v>4.699185751633195e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0009363113786093891</v>
+        <v>4.378069888844038e-07</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0004990325542166829</v>
+        <v>3.759037880968208e-08</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001471899216994643</v>
+        <v>6.508224004164731e-08</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.001865987898781896</v>
+        <v>1.647115084324469e-07</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.000137924769660458</v>
+        <v>2.558091694027098e-07</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001866891543613747</v>
+        <v>8.494706804640373e-08</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001668590703047812</v>
+        <v>4.824404413739103e-07</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0006168433465063572</v>
+        <v>1.241368892124228e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0004522317904047668</v>
+        <v>1.818844168610667e-07</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0004749832150992006</v>
+        <v>9.936153588796515e-08</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0008486862643621862</v>
+        <v>5.981981416880444e-07</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0008481759577989578</v>
+        <v>1.232932334005454e-07</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0006768445600755513</v>
+        <v>1.35101771547852e-07</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.00070065853651613</v>
+        <v>1.760982257792421e-07</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0005036906804889441</v>
+        <v>1.301093988104185e-07</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0002590251096989959</v>
+        <v>3.542503748121817e-07</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0003427329356782138</v>
+        <v>4.88413547827804e-07</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001109547913074493</v>
+        <v>3.38420761636371e-07</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0005982317379675806</v>
+        <v>1.121002668469373e-08</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0005044644931331277</v>
+        <v>4.663650088332361e-07</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0004032297292724252</v>
+        <v>1.137163749831416e-07</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0005622885655611753</v>
+        <v>5.857692713107099e-07</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.669088619062677e-05</v>
+        <v>4.340924135703972e-07</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0007087059784680605</v>
+        <v>5.568867891270202e-07</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001065918826498091</v>
+        <v>6.61073102037335e-07</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.001793490839190781</v>
+        <v>7.106336852302775e-08</v>
       </c>
       <c r="FS4" t="n">
-        <v>7.691406790399924e-05</v>
+        <v>5.248563184068189e-07</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002515854721423239</v>
+        <v>3.083610806697834e-07</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0006155159790068865</v>
+        <v>5.820771207254438e-07</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001975246996153146</v>
+        <v>1.031779532922883e-07</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0003428042982704937</v>
+        <v>1.047197997650073e-06</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0005381646915338933</v>
+        <v>2.165429435763144e-07</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001074974541552365</v>
+        <v>1.641354856474209e-07</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0005435377825051546</v>
+        <v>1.168404892837316e-07</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0007254458614625037</v>
+        <v>5.63433218303544e-07</v>
       </c>
       <c r="GB4" t="n">
-        <v>3.828576518571936e-05</v>
+        <v>1.111850789214941e-08</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.00143402605317533</v>
+        <v>6.828325922469958e-07</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001018236391246319</v>
+        <v>4.873617172052036e-07</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.002206650795415044</v>
+        <v>1.379234788601025e-07</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0005509741022251546</v>
+        <v>2.910153398261173e-07</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0005609260988421738</v>
+        <v>3.275190252338689e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0004114485345780849</v>
+        <v>9.403016143494369e-10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01918768882751465</v>
+        <v>3.034373419197323e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006426949403248727</v>
+        <v>9.494867114767658e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006328199524432421</v>
+        <v>3.526867464742622e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006696091964840889</v>
+        <v>7.682620761784165e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01350233890116215</v>
+        <v>8.446169985631968e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002049752278253436</v>
+        <v>3.716841057155307e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003461293876171112</v>
+        <v>4.505813500088607e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007532858871854842</v>
+        <v>1.106810465500985e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002138814190402627</v>
+        <v>3.48536532968069e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02012307569384575</v>
+        <v>8.679317708981671e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005104524898342788</v>
+        <v>1.433576635179179e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004376341588795185</v>
+        <v>1.256462134335834e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003429346717894077</v>
+        <v>1.313307684824849e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01283109560608864</v>
+        <v>1.432683482960329e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002030571456998587</v>
+        <v>4.570651412905136e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001362160197459161</v>
+        <v>8.737941037395558e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>9.080028394237161e-05</v>
+        <v>7.839897619987823e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006193647859618068</v>
+        <v>3.275449689255083e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001906975056044757</v>
+        <v>3.159156269916252e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001352664083242416</v>
+        <v>5.248108170263777e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002359450096264482</v>
+        <v>5.475428999091037e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001966845942661166</v>
+        <v>4.90419926890695e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009972804691642523</v>
+        <v>3.804585979594322e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001434200094081461</v>
+        <v>3.172160090159082e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001401817658916116</v>
+        <v>8.720064670342254e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001556666335090995</v>
+        <v>6.295953980384184e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001173616154119372</v>
+        <v>9.44181266504529e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0006113381823524833</v>
+        <v>1.598200349839374e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.00231273309327662</v>
+        <v>5.67267566253804e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001726792193949223</v>
+        <v>1.714686614917582e-09</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.739079693332314e-05</v>
+        <v>5.29501331669735e-10</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001511184498667717</v>
+        <v>2.202327209488431e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001071591395884752</v>
+        <v>8.395528716675926e-11</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001060290145687759</v>
+        <v>1.067044230751435e-08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001434365753084421</v>
+        <v>2.952899036401391e-09</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001709864591248333</v>
+        <v>2.381826291752986e-09</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002736398717388511</v>
+        <v>2.358687467562959e-09</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002178139518946409</v>
+        <v>3.853019236998989e-09</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.816443732939661e-05</v>
+        <v>4.24661505959989e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0004848113167099655</v>
+        <v>1.191533316458049e-09</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001539319171570241</v>
+        <v>2.265693743730424e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0004069649439770728</v>
+        <v>3.61399798975981e-11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0008780676871538162</v>
+        <v>1.455226605884263e-08</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001205221749842167</v>
+        <v>4.12847006581174e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001701746368780732</v>
+        <v>5.531735625119438e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0126097658649087</v>
+        <v>2.439171886692293e-08</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003141154767945409</v>
+        <v>1.29331212406214e-10</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001166163245216012</v>
+        <v>2.276959509828202e-09</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0009332795161753893</v>
+        <v>6.067724100944361e-11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.006218630820512772</v>
+        <v>1.623705081499338e-08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001591727486811578</v>
+        <v>3.003600701489972e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001610684557817876</v>
+        <v>2.929923192951378e-09</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001433810451999307</v>
+        <v>1.574250951819067e-09</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0003969703102484345</v>
+        <v>1.055285903106551e-08</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.004141759593039751</v>
+        <v>1.123501380817515e-08</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003496028715744615</v>
+        <v>5.328936403259377e-09</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0004458720504771918</v>
+        <v>4.797671593337327e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.006381033919751644</v>
+        <v>3.573552120883505e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.006669148802757263</v>
+        <v>1.30105815010495e-09</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001350391888990998</v>
+        <v>1.319885090111939e-09</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.000147113692946732</v>
+        <v>6.412263608979174e-09</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.000508161261677742</v>
+        <v>1.891597811720658e-08</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002018284052610397</v>
+        <v>6.418555131837422e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.003116320353001356</v>
+        <v>3.273143533988332e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0004209760809317231</v>
+        <v>2.083075489878183e-09</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0003418970154598355</v>
+        <v>5.566484606589484e-09</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001766958157531917</v>
+        <v>3.3307425706397e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001017375150695443</v>
+        <v>2.469813020766765e-09</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001314668450504541</v>
+        <v>2.536536314323712e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001104215974919498</v>
+        <v>1.436359697848388e-09</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0004591938923113048</v>
+        <v>6.659969464806181e-09</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0009462784510105848</v>
+        <v>5.622173837593891e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.007058268412947655</v>
+        <v>1.002564165020203e-08</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0006365124136209488</v>
+        <v>2.522290820650142e-09</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001821896410547197</v>
+        <v>8.363779002706906e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.839603570871986e-05</v>
+        <v>3.101332746169305e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001574613736011088</v>
+        <v>1.078132871867865e-08</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00028381691663526</v>
+        <v>2.602600135404032e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001936822081916034</v>
+        <v>3.108438839660721e-09</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001263176440261304</v>
+        <v>2.131640197688967e-09</v>
       </c>
       <c r="CD5" t="n">
-        <v>9.472529927734286e-05</v>
+        <v>1.097522073223445e-09</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003175440710037947</v>
+        <v>3.958544159132771e-09</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0005956478416919708</v>
+        <v>1.333912980072682e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.001199859892949462</v>
+        <v>4.352538884866419e-10</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.196968802716583e-05</v>
+        <v>4.090445759885597e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.002385966712608933</v>
+        <v>3.453942687414724e-09</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.001854262431152165</v>
+        <v>2.307560809100551e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0003169217961840332</v>
+        <v>1.617112443952351e-09</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0005193342221900821</v>
+        <v>2.510862406879255e-09</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004273850936442614</v>
+        <v>2.800830678495458e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001463396940380335</v>
+        <v>1.078057731973558e-08</v>
       </c>
       <c r="CO5" t="n">
-        <v>4.229496698826551e-05</v>
+        <v>4.626378724559288e-10</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.002532751299440861</v>
+        <v>7.351215192130667e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0007174386410042644</v>
+        <v>9.174076609497206e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0005053250933997333</v>
+        <v>1.317296405289881e-08</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.003608366707339883</v>
+        <v>3.987676855388145e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.003618482267484069</v>
+        <v>9.527088451477539e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001014366396702826</v>
+        <v>4.120821461839341e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>3.233435563743114e-08</v>
+        <v>6.489144777077627e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.002860636916011572</v>
+        <v>3.350788757572332e-09</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0003988859243690968</v>
+        <v>1.281669992359014e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001834547845646739</v>
+        <v>1.727490706038282e-09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001943433890119195</v>
+        <v>1.178909858623456e-09</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.002515849890187383</v>
+        <v>3.085473654351745e-09</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001747817266732454</v>
+        <v>7.541582913717093e-10</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0005984496674500406</v>
+        <v>7.164598359032937e-10</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0002049242466455325</v>
+        <v>1.786564118866352e-09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001450501382350922</v>
+        <v>5.555755855368716e-10</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.003934722859412432</v>
+        <v>8.480425250922963e-09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.000730897590983659</v>
+        <v>1.034160845847509e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.003434503450989723</v>
+        <v>1.688438389102487e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004628536757081747</v>
+        <v>1.233812696455061e-08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001056207809597254</v>
+        <v>8.460299127932558e-11</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001097644097171724</v>
+        <v>3.329783337946424e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002393016475252807</v>
+        <v>4.167759026785234e-09</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.002829128876328468</v>
+        <v>2.355433403877782e-09</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001324883778579533</v>
+        <v>1.993071707673266e-09</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.000260135333519429</v>
+        <v>1.838364127593195e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001782088191248477</v>
+        <v>1.72192038405683e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001566696912050247</v>
+        <v>8.548984631318035e-09</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001332675805315375</v>
+        <v>4.887846127843432e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.002192140556871891</v>
+        <v>1.489079193284226e-09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.000358184683136642</v>
+        <v>7.522688028060998e-10</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0004543178365565836</v>
+        <v>8.668024520375184e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0006591299897991121</v>
+        <v>3.883500188095468e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001053691026754677</v>
+        <v>1.181535869143602e-09</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.002243972849100828</v>
+        <v>3.066912723781456e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0004599059466272593</v>
+        <v>8.108735904954756e-11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0007227673777379096</v>
+        <v>5.719038576046387e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0012638681801036</v>
+        <v>9.662552979960992e-10</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001635499531403184</v>
+        <v>2.561887590957213e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001399305416271091</v>
+        <v>8.615287150348649e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001850030617788434</v>
+        <v>4.194754765762809e-09</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0003608114784583449</v>
+        <v>7.435376758735401e-10</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0003142931964248419</v>
+        <v>3.528594083590519e-12</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.003381718881428242</v>
+        <v>2.311488556117069e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.000594917219132185</v>
+        <v>7.816067792987269e-10</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0008626829367130995</v>
+        <v>9.463811956322843e-10</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0003580568300094455</v>
+        <v>3.69654307164069e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.002206745557487011</v>
+        <v>8.594074896173254e-10</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001821309793740511</v>
+        <v>3.495623346339016e-09</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0009859494166448712</v>
+        <v>2.820682576398781e-09</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.000575093668885529</v>
+        <v>8.273375318168519e-10</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001717116101644933</v>
+        <v>3.137747173198591e-09</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002496081870049238</v>
+        <v>3.112994750864573e-09</v>
       </c>
       <c r="EQ5" t="n">
-        <v>8.655490819364786e-05</v>
+        <v>2.993921111027475e-09</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.353646025061607e-05</v>
+        <v>3.253991520679733e-10</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0008528424659743905</v>
+        <v>1.051260856144154e-09</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001441182801499963</v>
+        <v>1.407709393497214e-09</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001607741927728057</v>
+        <v>3.354111210995825e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.002418855438008904</v>
+        <v>4.589721491754517e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001508862245827913</v>
+        <v>2.377973651324083e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0004395585565362126</v>
+        <v>1.249851555584769e-09</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002725999336689711</v>
+        <v>4.061535552324358e-09</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001117818173952401</v>
+        <v>9.236663101042097e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001185651984997094</v>
+        <v>2.02900229950842e-09</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0004289619100745767</v>
+        <v>1.807558769328921e-09</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.002598876133561134</v>
+        <v>2.964730239085611e-09</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.001725961570627987</v>
+        <v>9.284114033114577e-10</v>
       </c>
       <c r="FE5" t="n">
-        <v>8.882030670065433e-05</v>
+        <v>2.429630108213843e-10</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.000444556528236717</v>
+        <v>1.476625599572401e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>5.856553616467863e-05</v>
+        <v>2.602097703974238e-10</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001593307591974735</v>
+        <v>7.988481875997877e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0008002110989764333</v>
+        <v>6.975663380259789e-10</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.00349185336381197</v>
+        <v>6.941610397603881e-09</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0004460568015929312</v>
+        <v>5.305866856986086e-11</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0008070046314969659</v>
+        <v>6.856540224475793e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0005025360733270645</v>
+        <v>1.731362497814359e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0006505365017801523</v>
+        <v>3.290785199894231e-09</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0008129367488436401</v>
+        <v>1.445946695710632e-10</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001983694732189178</v>
+        <v>9.175947113249094e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003485818626359105</v>
+        <v>5.585909068628325e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0009641708456911147</v>
+        <v>6.518121153931133e-09</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001486828085035086</v>
+        <v>4.28156354814746e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002293313620612025</v>
+        <v>6.938554619750903e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0007175877690315247</v>
+        <v>2.651468600234352e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.001403732807375491</v>
+        <v>8.027813080957458e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002778902417048812</v>
+        <v>6.923136730563328e-09</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0007985194097273052</v>
+        <v>5.364222399606433e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.00282271602191031</v>
+        <v>1.772181568160391e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0003400736895855516</v>
+        <v>7.875629592923872e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>3.384120645932853e-05</v>
+        <v>1.338198885036945e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>5.215647979639471e-05</v>
+        <v>1.742554989192513e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001124921371228993</v>
+        <v>4.769534989179647e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0001370998070342466</v>
+        <v>3.824770500315822e-10</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.003596402239054441</v>
+        <v>3.403141324298531e-09</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001668764394707978</v>
+        <v>3.171772178234278e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0007535612676292658</v>
+        <v>2.609037430545413e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.10719674921711e-05</v>
+        <v>9.94686843114323e-07</v>
       </c>
       <c r="B6" t="n">
-        <v>9.99821349978447e-05</v>
+        <v>6.060356554371538e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.000764950731536e-05</v>
+        <v>3.976244897785364e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>3.274475966463797e-05</v>
+        <v>5.143736416357569e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>2.029370807576925e-05</v>
+        <v>7.930362357910781e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.661384158069268e-05</v>
+        <v>7.203749646578217e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.077239903679583e-05</v>
+        <v>1.204492832584947e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>8.183774298231583e-06</v>
+        <v>2.101173777191434e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.412117156491149e-06</v>
+        <v>2.754754291345307e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.906477700686082e-05</v>
+        <v>1.86663584145208e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>7.729518983978778e-05</v>
+        <v>6.191648026288021e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.729802074303734e-06</v>
+        <v>4.487336809688713e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.374601874384098e-05</v>
+        <v>6.811376806581393e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>2.940883132396266e-05</v>
+        <v>1.683174446043267e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>3.418114283704199e-05</v>
+        <v>6.55315670883283e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.477594923926517e-05</v>
+        <v>1.246514102604124e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.800414328405168e-06</v>
+        <v>1.510532570137002e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.09659617919533e-06</v>
+        <v>4.58421595794789e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>4.17471392211155e-06</v>
+        <v>6.296627930169052e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.55099987750873e-05</v>
+        <v>6.853819058960653e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>4.984302904631477e-06</v>
+        <v>1.146029944720794e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>5.588941348833032e-06</v>
+        <v>5.85307759592979e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.862603539848351e-06</v>
+        <v>1.53615280851227e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.550259366922546e-05</v>
+        <v>6.601832183150691e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.853587703721132e-06</v>
+        <v>3.497490297377226e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.367782806482865e-05</v>
+        <v>4.264676647380838e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.199168309540255e-05</v>
+        <v>1.487651815068602e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.963447958696634e-06</v>
+        <v>3.034600126738951e-07</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.084113046090351e-05</v>
+        <v>4.943322551298479e-07</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.376635155902477e-06</v>
+        <v>1.438824028809904e-06</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.138182480848627e-06</v>
+        <v>9.311690405411355e-07</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.813794364759815e-07</v>
+        <v>8.22826052626624e-07</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.837979081959929e-06</v>
+        <v>3.231279606552562e-06</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.314238584716804e-06</v>
+        <v>4.788588512383285e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.687579126359196e-06</v>
+        <v>2.45587102654099e-06</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.03861236514058e-06</v>
+        <v>7.500217407141463e-07</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.283519830205478e-06</v>
+        <v>8.43883412926516e-07</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.117486135626677e-05</v>
+        <v>1.344797283309163e-06</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.565893964856514e-06</v>
+        <v>1.476556576562871e-06</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.878247636952437e-06</v>
+        <v>1.278211584576638e-06</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.118023828894366e-05</v>
+        <v>6.119871187593162e-08</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.251586581929587e-06</v>
+        <v>9.507906497674412e-07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.952546426764457e-06</v>
+        <v>5.75731633034593e-07</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.895636038781959e-07</v>
+        <v>5.73911449919251e-07</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.105320037226193e-06</v>
+        <v>6.336177875709836e-07</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.678820682282094e-06</v>
+        <v>7.941687840684608e-08</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.320839747786522e-05</v>
+        <v>3.422775535000255e-06</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.461079126689583e-06</v>
+        <v>2.220867372670909e-06</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.280001924897078e-05</v>
+        <v>2.316911377420183e-06</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.26624375602114e-06</v>
+        <v>4.409645043779165e-06</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.079973480955232e-05</v>
+        <v>3.308460009066039e-06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.540518486668589e-06</v>
+        <v>4.489447746891528e-07</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.947055236290907e-06</v>
+        <v>9.007723065224127e-07</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.428317682439229e-05</v>
+        <v>9.26825293845468e-07</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.455099547660211e-06</v>
+        <v>6.027117649409774e-08</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.30922505579656e-05</v>
+        <v>6.022764864610508e-08</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.324238630535547e-05</v>
+        <v>2.033694727288093e-06</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.73502462025499e-06</v>
+        <v>5.261118758426164e-07</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.833496207837015e-05</v>
+        <v>3.277054702266469e-06</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.959733476222027e-06</v>
+        <v>9.160951321973698e-07</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.292435081268195e-05</v>
+        <v>3.563540360573825e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.941363714460749e-06</v>
+        <v>1.08057292891317e-06</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.391218681121245e-06</v>
+        <v>3.167629927247617e-07</v>
       </c>
       <c r="BL6" t="n">
-        <v>5.027989118389087e-06</v>
+        <v>3.518534867907874e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.056931250786874e-05</v>
+        <v>1.309046410824521e-06</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.345747114100959e-05</v>
+        <v>9.494760888628662e-07</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.934367775102146e-06</v>
+        <v>1.210789832839509e-06</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.093598439183552e-05</v>
+        <v>5.166846221982269e-07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.917414121839101e-06</v>
+        <v>1.574068505760806e-06</v>
       </c>
       <c r="BR6" t="n">
-        <v>4.139566044614185e-06</v>
+        <v>2.723871830312419e-07</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.359929223734071e-06</v>
+        <v>7.413487992380396e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.950347142264945e-06</v>
+        <v>4.140223097692797e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>2.855632601495017e-07</v>
+        <v>7.614412425027695e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.492786345304921e-05</v>
+        <v>2.837263764376985e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.812245480134152e-06</v>
+        <v>1.726325194795209e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>9.992959348892327e-06</v>
+        <v>2.312298420292791e-06</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.746193215192761e-06</v>
+        <v>1.301579345636128e-06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.966417352785356e-06</v>
+        <v>2.327362608411931e-06</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.188415343582164e-06</v>
+        <v>1.04813625512179e-06</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.149738295680436e-06</v>
+        <v>8.700391163074528e-08</v>
       </c>
       <c r="CC6" t="n">
-        <v>7.823336090950761e-06</v>
+        <v>4.666023869503988e-07</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.39201256135857e-07</v>
+        <v>1.676065011224637e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.65578840096714e-05</v>
+        <v>1.728304823700455e-06</v>
       </c>
       <c r="CF6" t="n">
-        <v>8.629182957520243e-06</v>
+        <v>9.122633173319628e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.033349917634041e-06</v>
+        <v>1.609512082723086e-06</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.901662471937016e-06</v>
+        <v>4.519319816154166e-07</v>
       </c>
       <c r="CI6" t="n">
-        <v>3.236976453990792e-06</v>
+        <v>1.783783773134928e-06</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.711376055231085e-06</v>
+        <v>1.964650309105309e-08</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.506093212810811e-06</v>
+        <v>6.567340165020141e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>4.95182712256792e-06</v>
+        <v>4.540248426110338e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.568676791270263e-05</v>
+        <v>1.023666186483752e-06</v>
       </c>
       <c r="CN6" t="n">
-        <v>8.595988219894934e-06</v>
+        <v>6.177874212198731e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>2.049823251581984e-06</v>
+        <v>2.650705027917866e-06</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.967139542102814e-05</v>
+        <v>6.929332698746293e-07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.126308870880166e-05</v>
+        <v>3.983701617471525e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>9.31814247451257e-06</v>
+        <v>8.651142024973524e-07</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.36003418447217e-05</v>
+        <v>6.595113291041343e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.030594921758166e-05</v>
+        <v>1.256800032933825e-06</v>
       </c>
       <c r="CU6" t="n">
-        <v>3.170745458191959e-06</v>
+        <v>2.787139408155781e-07</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.505621239379252e-07</v>
+        <v>3.712598584115767e-07</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.490524027758511e-05</v>
+        <v>1.609796868251578e-06</v>
       </c>
       <c r="CX6" t="n">
-        <v>9.643477824283764e-06</v>
+        <v>1.136117361966171e-06</v>
       </c>
       <c r="CY6" t="n">
-        <v>6.051625859981868e-06</v>
+        <v>1.570076392454212e-06</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.060313131049043e-06</v>
+        <v>3.895279121479689e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>3.583177203836385e-06</v>
+        <v>1.839393121372268e-06</v>
       </c>
       <c r="DB6" t="n">
-        <v>3.271209834565525e-06</v>
+        <v>4.227894834230028e-08</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.916970515798312e-06</v>
+        <v>7.183842853919487e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.506328312141704e-06</v>
+        <v>3.888122819262207e-07</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.059252372215269e-05</v>
+        <v>5.805371756650857e-07</v>
       </c>
       <c r="DF6" t="n">
-        <v>4.792912022821838e-07</v>
+        <v>2.491370651114266e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>9.558013971400214e-07</v>
+        <v>1.299033669965866e-06</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.223708386532962e-05</v>
+        <v>1.554090999889013e-06</v>
       </c>
       <c r="DI6" t="n">
-        <v>8.072574928519316e-06</v>
+        <v>1.205443140861462e-07</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.011935910355533e-05</v>
+        <v>3.683777094920515e-06</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.199529717472615e-06</v>
+        <v>5.456977305584587e-07</v>
       </c>
       <c r="DL6" t="n">
-        <v>4.946849685438792e-07</v>
+        <v>2.66624806499749e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>7.687888682994526e-06</v>
+        <v>6.709842068630678e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>2.390193003520835e-07</v>
+        <v>7.623578994753188e-07</v>
       </c>
       <c r="DO6" t="n">
-        <v>7.258478262883727e-08</v>
+        <v>5.673523446603213e-07</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.136346509156283e-05</v>
+        <v>1.65282585840032e-06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.011397034744732e-05</v>
+        <v>7.785451998643111e-07</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.395396667358e-06</v>
+        <v>2.465502006998577e-07</v>
       </c>
       <c r="DS6" t="n">
-        <v>2.867473540391074e-06</v>
+        <v>8.227834769058973e-07</v>
       </c>
       <c r="DT6" t="n">
-        <v>7.683223884669133e-06</v>
+        <v>7.77492857650941e-07</v>
       </c>
       <c r="DU6" t="n">
-        <v>2.497459945516312e-06</v>
+        <v>1.326285087088763e-06</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.644816843006993e-06</v>
+        <v>8.249336360677262e-07</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.828075937737594e-06</v>
+        <v>1.50950427268981e-07</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.447425711376127e-05</v>
+        <v>7.728153406105776e-08</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.876105650619138e-06</v>
+        <v>2.510732429072959e-06</v>
       </c>
       <c r="DZ6" t="n">
-        <v>9.34226363824564e-07</v>
+        <v>1.188579062727513e-06</v>
       </c>
       <c r="EA6" t="n">
-        <v>8.732904461794533e-06</v>
+        <v>4.942926352669019e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.021001025947044e-05</v>
+        <v>5.002153216082661e-07</v>
       </c>
       <c r="EC6" t="n">
-        <v>8.469883141515311e-07</v>
+        <v>6.647914574386959e-08</v>
       </c>
       <c r="ED6" t="n">
-        <v>2.784426897051162e-06</v>
+        <v>1.822274384721823e-06</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.025966184897698e-06</v>
+        <v>2.826557420121389e-06</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.836706011701608e-06</v>
+        <v>8.117265224427683e-07</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.343131771136541e-05</v>
+        <v>1.211607241202728e-06</v>
       </c>
       <c r="EH6" t="n">
-        <v>7.492658824048704e-06</v>
+        <v>7.710290219620219e-07</v>
       </c>
       <c r="EI6" t="n">
-        <v>3.358036337886006e-06</v>
+        <v>1.035923560266383e-06</v>
       </c>
       <c r="EJ6" t="n">
-        <v>4.687429282057565e-06</v>
+        <v>5.013647452756231e-08</v>
       </c>
       <c r="EK6" t="n">
-        <v>1.096072537620785e-06</v>
+        <v>1.349677972939389e-06</v>
       </c>
       <c r="EL6" t="n">
-        <v>6.170660526549909e-06</v>
+        <v>2.490651809239353e-07</v>
       </c>
       <c r="EM6" t="n">
-        <v>1.250132754648803e-06</v>
+        <v>5.407927972100879e-08</v>
       </c>
       <c r="EN6" t="n">
-        <v>3.015637503267499e-06</v>
+        <v>1.684257711076498e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>4.156811428401852e-07</v>
+        <v>5.946343435425661e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>8.312551472045016e-06</v>
+        <v>1.010636083265126e-06</v>
       </c>
       <c r="EQ6" t="n">
-        <v>7.751406883471645e-06</v>
+        <v>1.103306090044498e-06</v>
       </c>
       <c r="ER6" t="n">
-        <v>6.719848897773772e-06</v>
+        <v>4.818113552573777e-07</v>
       </c>
       <c r="ES6" t="n">
-        <v>7.553771865786985e-06</v>
+        <v>1.272557142328878e-06</v>
       </c>
       <c r="ET6" t="n">
-        <v>7.723604539933149e-06</v>
+        <v>5.556379392146482e-07</v>
       </c>
       <c r="EU6" t="n">
-        <v>1.426467406417942e-05</v>
+        <v>3.085794730850466e-07</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.872669781732839e-05</v>
+        <v>7.436767077706463e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>3.008016392413992e-06</v>
+        <v>1.161507270808215e-06</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.747706503214431e-06</v>
+        <v>4.037791541122715e-07</v>
       </c>
       <c r="EY6" t="n">
-        <v>1.508567038399633e-05</v>
+        <v>1.897871356959513e-06</v>
       </c>
       <c r="EZ6" t="n">
-        <v>6.7890141508542e-06</v>
+        <v>9.19485842132417e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>3.450335043453379e-06</v>
+        <v>1.851887645898387e-06</v>
       </c>
       <c r="FB6" t="n">
-        <v>1.911760364237125e-06</v>
+        <v>3.239762520479417e-07</v>
       </c>
       <c r="FC6" t="n">
-        <v>3.641751845862018e-06</v>
+        <v>1.580288540026231e-06</v>
       </c>
       <c r="FD6" t="n">
-        <v>5.525836968445219e-06</v>
+        <v>1.839149774696125e-07</v>
       </c>
       <c r="FE6" t="n">
-        <v>5.099884674564237e-07</v>
+        <v>6.286952043410565e-07</v>
       </c>
       <c r="FF6" t="n">
-        <v>5.614325345959514e-06</v>
+        <v>8.961061581658214e-08</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.392366241110722e-06</v>
+        <v>1.15234925601726e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>2.599818571979995e-06</v>
+        <v>1.88641092790931e-06</v>
       </c>
       <c r="FI6" t="n">
-        <v>1.12987127067754e-05</v>
+        <v>2.181603122153319e-06</v>
       </c>
       <c r="FJ6" t="n">
-        <v>1.070493908628123e-05</v>
+        <v>1.427000825060531e-06</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.98018790090282e-06</v>
+        <v>1.611302650417201e-06</v>
       </c>
       <c r="FL6" t="n">
-        <v>2.086943140966468e-06</v>
+        <v>1.685126562733785e-06</v>
       </c>
       <c r="FM6" t="n">
-        <v>3.751349595404463e-07</v>
+        <v>5.447421358439897e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>9.3407807071344e-06</v>
+        <v>1.599476945557399e-06</v>
       </c>
       <c r="FO6" t="n">
-        <v>1.056011933542322e-05</v>
+        <v>2.420570353933726e-06</v>
       </c>
       <c r="FP6" t="n">
-        <v>9.428879820916336e-06</v>
+        <v>1.910293576656841e-06</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.367740060231881e-05</v>
+        <v>3.582671752155875e-06</v>
       </c>
       <c r="FR6" t="n">
-        <v>1.210317009281425e-06</v>
+        <v>1.133419345933362e-06</v>
       </c>
       <c r="FS6" t="n">
-        <v>2.714552465477027e-06</v>
+        <v>2.667777835085872e-06</v>
       </c>
       <c r="FT6" t="n">
-        <v>7.404445568681695e-06</v>
+        <v>5.561519174079876e-07</v>
       </c>
       <c r="FU6" t="n">
-        <v>1.400892870151438e-06</v>
+        <v>5.996561469601147e-08</v>
       </c>
       <c r="FV6" t="n">
-        <v>1.420858552592108e-05</v>
+        <v>8.039395424930262e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>4.48874561698176e-06</v>
+        <v>3.274034497735556e-06</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.957987589979894e-06</v>
+        <v>6.977051612011564e-07</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.570873791933991e-05</v>
+        <v>5.939332936577557e-07</v>
       </c>
       <c r="FZ6" t="n">
-        <v>3.953422947233776e-06</v>
+        <v>1.953869315229895e-07</v>
       </c>
       <c r="GA6" t="n">
-        <v>1.696618028290686e-06</v>
+        <v>2.381897957093315e-06</v>
       </c>
       <c r="GB6" t="n">
-        <v>2.191751718783053e-06</v>
+        <v>1.095299239750602e-06</v>
       </c>
       <c r="GC6" t="n">
-        <v>2.813612809404731e-06</v>
+        <v>2.944959760498023e-06</v>
       </c>
       <c r="GD6" t="n">
-        <v>9.695774679130409e-06</v>
+        <v>2.163660610676743e-06</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.535483145038597e-05</v>
+        <v>7.80849745751766e-07</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.763172463142837e-06</v>
+        <v>1.413077939105278e-07</v>
       </c>
       <c r="GG6" t="n">
-        <v>6.97407642746839e-07</v>
+        <v>3.719372330124315e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0009701354429125786</v>
+        <v>1.075887212209636e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009604325518012047</v>
+        <v>5.576624062086921e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001115888240747154</v>
+        <v>1.938586819960619e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003197414567694068</v>
+        <v>2.154441290258546e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001679485198110342</v>
+        <v>1.722968363537802e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005688230972737074</v>
+        <v>9.462176421948243e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003115094441454858</v>
+        <v>7.37155801289191e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002748507773503661</v>
+        <v>1.460885755477648e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000777407840359956</v>
+        <v>6.136754109320464e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001627134624868631</v>
+        <v>5.394911681833037e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009102932177484035</v>
+        <v>6.411643880710471e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001956158957909793</v>
+        <v>2.86846875496849e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002238622400909662</v>
+        <v>3.849776476272382e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001044434611685574</v>
+        <v>2.22869834942685e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005297801923006773</v>
+        <v>1.139454343501711e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>6.68403081363067e-05</v>
+        <v>4.771166572936636e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0006302117835730314</v>
+        <v>4.464673679649422e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001058178022503853</v>
+        <v>2.707135422497231e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002687817323021591</v>
+        <v>1.237756237060239e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0006930741365067661</v>
+        <v>9.317794251728628e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001735817641019821</v>
+        <v>3.75124443507957e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009410663042217493</v>
+        <v>2.368090463278349e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003598048351705074</v>
+        <v>1.319161242463451e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001458681072108448</v>
+        <v>1.804315843401127e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004966632695868611</v>
+        <v>6.618213319597999e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001030102954246104</v>
+        <v>1.757006884872681e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0006222024094313383</v>
+        <v>7.415413278977212e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.690836304798722e-05</v>
+        <v>1.519829538665363e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0002669008099474013</v>
+        <v>8.867011729307706e-07</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001897201291285455</v>
+        <v>1.564035187584523e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0005680675385519862</v>
+        <v>1.498660708421085e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0008335565216839314</v>
+        <v>1.505831960457726e-06</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.482077540364116e-05</v>
+        <v>1.319465354754357e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002592517994344234</v>
+        <v>5.423013931249443e-07</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.018539478536695e-06</v>
+        <v>4.237795110384468e-06</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9.722755930852145e-05</v>
+        <v>6.646275778621202e-07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001576589653268456</v>
+        <v>1.549638113829133e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0005588599597103894</v>
+        <v>1.383859171255608e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.156873132567853e-05</v>
+        <v>9.268140388485335e-07</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0005653909174725413</v>
+        <v>1.429188273505133e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0001342766045127064</v>
+        <v>4.67324952069248e-07</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001366726821288466</v>
+        <v>1.017901468003402e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0004798113368451595</v>
+        <v>3.26745976053644e-07</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0005515182856470346</v>
+        <v>2.264619070047047e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001139020314440131</v>
+        <v>8.266648023891321e-07</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0001718962739687413</v>
+        <v>7.467547789019591e-07</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.005405779927968979</v>
+        <v>6.341152584354859e-06</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001136324601247907</v>
+        <v>2.363508428970817e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0002846708230208606</v>
+        <v>9.275876209358103e-07</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0005949418991804123</v>
+        <v>1.431052510270092e-06</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002769872080534697</v>
+        <v>6.766473688912811e-06</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001260015182197094</v>
+        <v>1.735900809762825e-07</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001175892073661089</v>
+        <v>1.01831619758741e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001587255159392953</v>
+        <v>2.721369583014166e-07</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0004877161700278521</v>
+        <v>1.802625320124207e-07</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.002133029978722334</v>
+        <v>1.210869982060103e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.002761630108579993</v>
+        <v>1.098341499528033e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.000284351030131802</v>
+        <v>8.054726663431211e-07</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001098690438084304</v>
+        <v>1.727057792777487e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001605529338121414</v>
+        <v>1.219514160766266e-07</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.52462744154036e-05</v>
+        <v>1.034730075843981e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001101946458220482</v>
+        <v>1.1769404864026e-06</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0008077926468104124</v>
+        <v>1.622181571292458e-07</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0006987756351009011</v>
+        <v>3.404762196623778e-07</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.001478252583183348</v>
+        <v>2.314443236173247e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0010954454774037</v>
+        <v>4.316231354550837e-07</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0002463160490151495</v>
+        <v>1.775468945197645e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.000528714619576931</v>
+        <v>1.046735860654735e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0002623579348437488</v>
+        <v>5.338425239642675e-07</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0004972167080268264</v>
+        <v>6.600298547709826e-07</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0004996452480554581</v>
+        <v>7.963014923006995e-07</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0005605184705927968</v>
+        <v>1.186130248242989e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0001836537558119744</v>
+        <v>6.160312295833137e-07</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.003038821974769235</v>
+        <v>3.449136329436442e-06</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0008422142127528787</v>
+        <v>1.858917073604971e-07</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.126599429175258e-05</v>
+        <v>1.4695374375151e-06</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0002792668237816542</v>
+        <v>3.905702214979101e-07</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0009723622351884842</v>
+        <v>4.357383659225889e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0003059084992855787</v>
+        <v>1.747596002132923e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0005816867342218757</v>
+        <v>8.728745797270676e-07</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.000608172093052417</v>
+        <v>8.509196192107993e-08</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0002458007365930825</v>
+        <v>1.456944005440164e-07</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001758288708515465</v>
+        <v>2.113552227456239e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0006692152237519622</v>
+        <v>4.680426854974939e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0004222806601319462</v>
+        <v>6.2298869352162e-07</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004380503669381142</v>
+        <v>2.091748569910123e-07</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0005271192057989538</v>
+        <v>2.299637571923085e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0005502881249412894</v>
+        <v>2.784449861792382e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0005283187492750585</v>
+        <v>3.069804961342015e-07</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0006280138622969389</v>
+        <v>4.408107656672655e-09</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.00192407111171633</v>
+        <v>1.223872232003487e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0007219365215860307</v>
+        <v>2.246370968350675e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0001513695606263354</v>
+        <v>1.94399422071001e-06</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.002327614696696401</v>
+        <v>1.679160391176993e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0009185540839098394</v>
+        <v>3.197596356585564e-07</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.002380330814048648</v>
+        <v>8.909424877856509e-07</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.001822997815907001</v>
+        <v>2.267900981678395e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.001214488060213625</v>
+        <v>2.057700612567714e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0005251644179224968</v>
+        <v>4.263442860974465e-07</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0002105346939060837</v>
+        <v>4.253024599165656e-07</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001679147011600435</v>
+        <v>1.961930138349999e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0008006749558262527</v>
+        <v>7.579031375826162e-07</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0008245763019658625</v>
+        <v>1.04133516742877e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0003101426700595766</v>
+        <v>6.616693326577661e-08</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0005160181317478418</v>
+        <v>2.557178731876775e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0004778391448780894</v>
+        <v>9.390021205035737e-09</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001026306068524718</v>
+        <v>4.559209116905549e-07</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0005845666746608913</v>
+        <v>2.394677949268953e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001068409532308578</v>
+        <v>2.565284660249745e-07</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0007298764539882541</v>
+        <v>3.315071353426902e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.074798587476835e-05</v>
+        <v>1.852454488471267e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001832218375056982</v>
+        <v>6.083366770326393e-07</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002144624479115009</v>
+        <v>1.517535110906465e-07</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001314613269641995</v>
+        <v>2.007444209084497e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.00151070870924741</v>
+        <v>9.835568448579579e-08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.001732890610583127</v>
+        <v>3.149870963170542e-06</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.002124774502590299</v>
+        <v>1.808933348002029e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0005239585880190134</v>
+        <v>6.969938795009512e-07</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0008141485159285367</v>
+        <v>2.430233962513739e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0005928601021878421</v>
+        <v>2.140679100648413e-07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001083167036995292</v>
+        <v>9.875540172288311e-07</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0004432066925801337</v>
+        <v>8.094281156445504e-07</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0009893388487398624</v>
+        <v>1.882364358607447e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0005398141220211983</v>
+        <v>2.471214202159899e-07</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0005149461212567985</v>
+        <v>2.84544080386695e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0001568575098644942</v>
+        <v>1.908241102910324e-07</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0001057341578416526</v>
+        <v>3.752627435460454e-07</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0005907014710828662</v>
+        <v>4.53745656159299e-07</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0007667795289307833</v>
+        <v>2.63840297520801e-06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0007384615018963814</v>
+        <v>7.402437063319667e-08</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0007199648534879088</v>
+        <v>9.172558748105075e-07</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0002655332791619003</v>
+        <v>8.403424089920009e-07</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004966269480064511</v>
+        <v>9.189743650495075e-07</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0003736013313755393</v>
+        <v>1.086056386156997e-06</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.001574760070070624</v>
+        <v>2.674413281056331e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001184914726763964</v>
+        <v>1.363196986403636e-07</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.002043906366452575</v>
+        <v>2.405413113137911e-08</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.001066419878043234</v>
+        <v>1.673720930739364e-07</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0002514073858037591</v>
+        <v>1.646371288188675e-07</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0006362129934132099</v>
+        <v>7.828903108020313e-07</v>
       </c>
       <c r="EK7" t="n">
-        <v>7.352387183345854e-05</v>
+        <v>7.510205932703684e-07</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0006580034387297928</v>
+        <v>1.083734701978756e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>4.489329512580298e-05</v>
+        <v>3.938302768347057e-07</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0002251179685117677</v>
+        <v>8.979066024039639e-07</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.000324848952004686</v>
+        <v>1.362382135994267e-07</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0009418361587449908</v>
+        <v>1.050582568495884e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0006682297680526972</v>
+        <v>6.047357032912259e-07</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.001064617186784744</v>
+        <v>1.942109747687937e-06</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001056577428244054</v>
+        <v>1.725220727166743e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0007271213689818978</v>
+        <v>1.09340973608596e-07</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.001503873849287629</v>
+        <v>1.694139655228355e-07</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.002222892362624407</v>
+        <v>7.806995085957169e-07</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0003769594477489591</v>
+        <v>7.966728503561171e-07</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0004046461835969239</v>
+        <v>1.84110604095622e-07</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.001574873691424727</v>
+        <v>2.214359483332373e-06</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0006044370238669217</v>
+        <v>4.373366664367495e-07</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0002753266890067607</v>
+        <v>1.117765236813284e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0003247728454880416</v>
+        <v>3.38788709086657e-07</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0003674113540910184</v>
+        <v>2.529707671783399e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0008127043838612735</v>
+        <v>7.017602001724299e-07</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0008382769883610308</v>
+        <v>5.182985205465229e-07</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0008035777718760073</v>
+        <v>6.339795390886138e-07</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0004367440124042332</v>
+        <v>4.850955548363345e-08</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0003092852130066603</v>
+        <v>1.250260311280726e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001090705743990839</v>
+        <v>1.645928023208398e-06</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.001526233972981572</v>
+        <v>1.562485294925864e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0005751614226028323</v>
+        <v>1.622315153326781e-07</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.000941618112847209</v>
+        <v>3.053371528949356e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0004587679286487401</v>
+        <v>3.050207340038469e-07</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0005673391278833151</v>
+        <v>2.967215323224082e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0004767547070514411</v>
+        <v>2.301889480804675e-06</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.001324725337326527</v>
+        <v>1.818964165067882e-06</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0007145166746340692</v>
+        <v>1.450577428840916e-06</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001399344066157937</v>
+        <v>1.142898327088915e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>9.266204142477363e-05</v>
+        <v>1.987687028304208e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>8.615216938778758e-05</v>
+        <v>7.392333145617158e-07</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0009686099947430193</v>
+        <v>2.258845597680192e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0002304718655068427</v>
+        <v>1.1090203315689e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0006086883367970586</v>
+        <v>4.645328772312496e-06</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0002546547038946301</v>
+        <v>9.712073278933531e-07</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.001562372781336308</v>
+        <v>8.074916308942193e-07</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0005209972732700408</v>
+        <v>5.049172955295944e-07</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0007191795157268643</v>
+        <v>2.164774286939064e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0003463973989710212</v>
+        <v>4.299171862953699e-08</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0003893329994753003</v>
+        <v>3.67107531928923e-06</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.001026365207508206</v>
+        <v>1.464024762753979e-06</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001786727458238602</v>
+        <v>7.21858668839559e-07</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0004647508321795613</v>
+        <v>1.147850639426906e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0008167214691638947</v>
+        <v>5.07516006109654e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0001494737662142143</v>
+        <v>2.136881116499012e-09</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002446293365210295</v>
+        <v>1.193039089741887e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.974093851866201e-05</v>
+        <v>3.348997079655192e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009787733433768153</v>
+        <v>2.935773402157338e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001081348513253033</v>
+        <v>4.096194050617896e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001439049956388772</v>
+        <v>1.442634811610333e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001246899773832411</v>
+        <v>2.974793522625419e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003734492347575724</v>
+        <v>2.227259709997043e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006131588015705347</v>
+        <v>5.628140620217437e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002148223866242915</v>
+        <v>5.025709293171587e-10</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002655150601640344</v>
+        <v>1.406553806759803e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001485563989263028</v>
+        <v>6.596182267060158e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003850022039841861</v>
+        <v>9.989454596848191e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004310965887270868</v>
+        <v>7.471863128216683e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001176768564619124</v>
+        <v>1.969814888980181e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.122462319675833e-05</v>
+        <v>9.644050003032589e-10</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.053680484299548e-05</v>
+        <v>8.15907341689126e-11</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0004525922704488039</v>
+        <v>5.392260415959527e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>3.715787170222029e-05</v>
+        <v>2.544879862398375e-10</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003246035485062748</v>
+        <v>3.328645137301578e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002534579252824187</v>
+        <v>1.097155144513806e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000207658318686299</v>
+        <v>1.245115344161718e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001211023045470938</v>
+        <v>2.757722494806103e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>3.57916796929203e-05</v>
+        <v>3.605164167197472e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001132151955971494</v>
+        <v>3.917106639050871e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.309822492767125e-05</v>
+        <v>2.501840512536546e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0002684836217667907</v>
+        <v>2.363079065759166e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.009759428910911e-05</v>
+        <v>5.142167136540365e-09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0001206518281833269</v>
+        <v>1.478253741638014e-09</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0005275656003504992</v>
+        <v>1.038323316215894e-09</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001153243792941794</v>
+        <v>5.009568759817284e-09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0001305964105995372</v>
+        <v>4.911440143473556e-09</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002377025230089203</v>
+        <v>7.944819913063839e-09</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002414309710729867</v>
+        <v>1.948762706760476e-09</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.914986731018871e-05</v>
+        <v>1.278517114400302e-08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001180021281470545</v>
+        <v>1.40528499947834e-09</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0003281502577010542</v>
+        <v>3.893167732638148e-10</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.000439020135672763</v>
+        <v>3.269676085437823e-09</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0003340755065437406</v>
+        <v>4.870748249174994e-11</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.989996472839266e-05</v>
+        <v>4.603295522542794e-11</v>
       </c>
       <c r="AO8" t="n">
-        <v>3.390986239537597e-05</v>
+        <v>1.631507595689641e-09</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0002010009920923039</v>
+        <v>1.76274206342697e-09</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001144615889643319</v>
+        <v>3.088719946475749e-09</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.353205127292313e-05</v>
+        <v>2.875130800106263e-09</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.421188689069822e-05</v>
+        <v>9.140641021865292e-10</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0001583002303959802</v>
+        <v>2.499563223068435e-09</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001688916934654117</v>
+        <v>1.381407699341253e-08</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0005525825545191765</v>
+        <v>2.268671028815561e-09</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0002853049954865128</v>
+        <v>7.037427862677248e-10</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.787104889051989e-05</v>
+        <v>1.146122130535332e-08</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0005673845880664885</v>
+        <v>1.39025368994794e-08</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0001912144216476008</v>
+        <v>3.823833250038433e-09</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.557666812208481e-05</v>
+        <v>4.218024818314348e-10</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0001512092421762645</v>
+        <v>1.284655382072231e-09</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.414271436166018e-05</v>
+        <v>2.587994041292063e-09</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0004757323185913265</v>
+        <v>1.973892160833657e-09</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0003949769306927919</v>
+        <v>5.183905749106543e-09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.451834006933495e-07</v>
+        <v>5.826303439704361e-09</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0008698946330696344</v>
+        <v>3.754013100376596e-09</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0006676186458207667</v>
+        <v>7.425616788125922e-10</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0002292600111104548</v>
+        <v>1.261393434148772e-09</v>
       </c>
       <c r="BJ8" t="n">
-        <v>5.215279452386312e-05</v>
+        <v>4.733853309346614e-09</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.275978325400501e-05</v>
+        <v>6.797814311454431e-09</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003853965317830443</v>
+        <v>1.706990104821671e-11</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0003390906204003841</v>
+        <v>3.507860668605645e-09</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.517234527971596e-05</v>
+        <v>2.87536827681123e-10</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0001620765106054023</v>
+        <v>7.641647870038071e-10</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002977030526380986</v>
+        <v>3.027559314361383e-09</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.237347820890136e-05</v>
+        <v>1.400329074918716e-09</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0001389801473123953</v>
+        <v>3.287608851820778e-09</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.943246550392359e-05</v>
+        <v>1.844986274868177e-09</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.665760156465694e-05</v>
+        <v>5.358800958532584e-09</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0001127606374211609</v>
+        <v>5.516927470416988e-10</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001045890268869698</v>
+        <v>7.993502748604442e-09</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0002199150912929326</v>
+        <v>9.244194298929642e-11</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002228718367405236</v>
+        <v>5.817191173207448e-10</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.133165829349309e-05</v>
+        <v>2.799818155097e-09</v>
       </c>
       <c r="BZ8" t="n">
-        <v>6.866040348540992e-05</v>
+        <v>9.530085165465607e-09</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.115713141392916e-05</v>
+        <v>2.373644392150709e-09</v>
       </c>
       <c r="CB8" t="n">
-        <v>1.096292362490203e-05</v>
+        <v>1.631453638850644e-09</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.471090556355193e-05</v>
+        <v>1.025205698113041e-09</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.353349115466699e-05</v>
+        <v>8.239919857544464e-10</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0004220972768962383</v>
+        <v>4.095512373680776e-09</v>
       </c>
       <c r="CF8" t="n">
-        <v>9.319908713223413e-06</v>
+        <v>4.474143000532393e-10</v>
       </c>
       <c r="CG8" t="n">
-        <v>9.703930845716968e-05</v>
+        <v>8.636471537926127e-10</v>
       </c>
       <c r="CH8" t="n">
-        <v>4.694989183917642e-05</v>
+        <v>9.007781187619912e-10</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0003036055713891983</v>
+        <v>3.526708258760891e-09</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0001695976970950142</v>
+        <v>7.115132788504397e-11</v>
       </c>
       <c r="CK8" t="n">
-        <v>2.106471220031381e-05</v>
+        <v>1.654619774527077e-09</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0001017246977426112</v>
+        <v>2.040493329857895e-09</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0005903225392103195</v>
+        <v>7.363935017323797e-10</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002963909937534481</v>
+        <v>3.362528921968533e-09</v>
       </c>
       <c r="CO8" t="n">
-        <v>9.378703543916345e-05</v>
+        <v>5.072601005906563e-09</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0003488504735287279</v>
+        <v>7.181418126833705e-09</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0003208591369912028</v>
+        <v>1.234561786134236e-09</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0001738461432978511</v>
+        <v>4.874763703810459e-09</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0005934673827141523</v>
+        <v>1.644268277090077e-09</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.000351415976183489</v>
+        <v>5.706088046508739e-09</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001103842805605382</v>
+        <v>1.147312356231112e-09</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.178776528831804e-06</v>
+        <v>9.479094176256808e-10</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0003914552507922053</v>
+        <v>3.852539620652351e-09</v>
       </c>
       <c r="CX8" t="n">
-        <v>3.388590266695246e-05</v>
+        <v>7.539777691079053e-10</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001864323858171701</v>
+        <v>2.063960558018607e-09</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0001000271295197308</v>
+        <v>1.72065484083106e-09</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0003284465637989342</v>
+        <v>4.566633737823622e-09</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001901722134789452</v>
+        <v>4.753250570921352e-10</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0001229946501553059</v>
+        <v>1.827580753399616e-09</v>
       </c>
       <c r="DD8" t="n">
-        <v>6.418267003027722e-05</v>
+        <v>1.684255734879514e-09</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0003013129171449691</v>
+        <v>1.498144275302593e-09</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0003479568404145539</v>
+        <v>2.603453230776154e-09</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.165958671364933e-05</v>
+        <v>9.246701182519246e-10</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0007221517735160887</v>
+        <v>1.474374400345368e-09</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0006257729837670922</v>
+        <v>5.665711233504567e-10</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0003586115490179509</v>
+        <v>3.504058376790908e-09</v>
       </c>
       <c r="DK8" t="n">
-        <v>8.872708713170141e-05</v>
+        <v>4.88066809190002e-10</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0002660131722223014</v>
+        <v>5.546811898682336e-09</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0003036274865735322</v>
+        <v>1.460928489294133e-09</v>
       </c>
       <c r="DN8" t="n">
-        <v>6.213942833710462e-05</v>
+        <v>1.241559965947658e-09</v>
       </c>
       <c r="DO8" t="n">
-        <v>6.732667679898441e-05</v>
+        <v>9.230862740849943e-10</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0001528332650195807</v>
+        <v>8.925565841977345e-10</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.000139095529448241</v>
+        <v>1.6367310839982e-09</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001843343779910356</v>
+        <v>1.997021437105673e-09</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0001357072760583833</v>
+        <v>1.976308006135241e-09</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0001214835501741618</v>
+        <v>2.403161225572603e-09</v>
       </c>
       <c r="DU8" t="n">
-        <v>8.568483463022858e-05</v>
+        <v>5.297632110767836e-09</v>
       </c>
       <c r="DV8" t="n">
-        <v>9.519719606032595e-05</v>
+        <v>2.8800242191096e-09</v>
       </c>
       <c r="DW8" t="n">
-        <v>3.095097781624645e-05</v>
+        <v>7.472504837124916e-10</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0002472720225341618</v>
+        <v>2.986513258917967e-09</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.578604032052681e-05</v>
+        <v>3.663813918919345e-09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.835945583181456e-05</v>
+        <v>3.298966433362693e-09</v>
       </c>
       <c r="EA8" t="n">
-        <v>6.448875501519069e-05</v>
+        <v>1.799597248997031e-09</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002802668313961476</v>
+        <v>6.418277020969754e-11</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0001382373739033937</v>
+        <v>1.232369095660601e-09</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0002433759364066646</v>
+        <v>4.992446012153096e-09</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0003781747946050018</v>
+        <v>3.638330081656704e-09</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0002091274654958397</v>
+        <v>5.717837869845255e-10</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0005201702588237822</v>
+        <v>1.471247235151907e-09</v>
       </c>
       <c r="EH8" t="n">
-        <v>4.249293488101102e-05</v>
+        <v>1.604152477518994e-09</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001093792961910367</v>
+        <v>7.288734060750812e-10</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0001641763665247709</v>
+        <v>2.937937670921542e-10</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0002633625408634543</v>
+        <v>3.201328091506639e-11</v>
       </c>
       <c r="EL8" t="n">
-        <v>5.937724927207455e-05</v>
+        <v>2.501494567042073e-10</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001964963594218716</v>
+        <v>7.310915761671311e-11</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001451767020625994</v>
+        <v>4.287354637977359e-10</v>
       </c>
       <c r="EO8" t="n">
-        <v>9.043469617608935e-06</v>
+        <v>9.249604415728641e-10</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0003915673296432942</v>
+        <v>2.942480259449098e-09</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0001283820456592366</v>
+        <v>1.685097061887575e-10</v>
       </c>
       <c r="ER8" t="n">
-        <v>3.239944635424763e-05</v>
+        <v>2.422771427923465e-10</v>
       </c>
       <c r="ES8" t="n">
-        <v>7.610389729961753e-05</v>
+        <v>5.716858098026023e-10</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0002060653787339106</v>
+        <v>4.814213028225822e-09</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0002340237842872739</v>
+        <v>1.97637062271383e-09</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0004668625770136714</v>
+        <v>1.790549930547058e-09</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0001649961050134152</v>
+        <v>2.058652692760177e-10</v>
       </c>
       <c r="EX8" t="n">
-        <v>6.639016646659002e-05</v>
+        <v>7.154365433414966e-10</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0003905025369022042</v>
+        <v>4.460679825513125e-09</v>
       </c>
       <c r="EZ8" t="n">
-        <v>9.791081538423896e-05</v>
+        <v>3.689240579696218e-11</v>
       </c>
       <c r="FA8" t="n">
-        <v>8.59081483213231e-05</v>
+        <v>2.154606271176362e-09</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0001474047021474689</v>
+        <v>5.648590484241822e-10</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0003163318615406752</v>
+        <v>3.205574472531225e-09</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0001609021710464731</v>
+        <v>3.019128835823892e-10</v>
       </c>
       <c r="FE8" t="n">
-        <v>5.027140650781803e-05</v>
+        <v>4.900162497989413e-10</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0001055804023053497</v>
+        <v>3.380256075047328e-10</v>
       </c>
       <c r="FG8" t="n">
-        <v>6.168817344587296e-05</v>
+        <v>8.275174434579924e-10</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0001469530543545261</v>
+        <v>3.217730304427846e-09</v>
       </c>
       <c r="FI8" t="n">
-        <v>7.214845390990376e-05</v>
+        <v>2.80245604500351e-09</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0004322546301409602</v>
+        <v>1.969507446020202e-09</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0002130531065631658</v>
+        <v>8.876643864397238e-10</v>
       </c>
       <c r="FL8" t="n">
-        <v>7.269291381817311e-05</v>
+        <v>8.307567078702505e-09</v>
       </c>
       <c r="FM8" t="n">
-        <v>7.024141086731106e-05</v>
+        <v>7.395717926961254e-10</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0001282273879041895</v>
+        <v>2.397514853313965e-09</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0001839776814449579</v>
+        <v>8.829556641387626e-09</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0002999687567353249</v>
+        <v>5.76856673539794e-10</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.000258497369941324</v>
+        <v>5.682349257796204e-09</v>
       </c>
       <c r="FR8" t="n">
-        <v>3.065062628593296e-05</v>
+        <v>6.372505634288927e-09</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0001948139251908287</v>
+        <v>4.149521282137414e-10</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0006783086573705077</v>
+        <v>1.077986233610773e-08</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0001584257843205705</v>
+        <v>2.969557932885891e-09</v>
       </c>
       <c r="FV8" t="n">
-        <v>8.01302376203239e-05</v>
+        <v>1.551442974090378e-09</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.000516046246048063</v>
+        <v>5.705919736698206e-09</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0001752520038280636</v>
+        <v>1.131028604106632e-09</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0002473206259310246</v>
+        <v>5.111353562625709e-10</v>
       </c>
       <c r="FZ8" t="n">
-        <v>3.540032776072621e-05</v>
+        <v>3.28603366739344e-10</v>
       </c>
       <c r="GA8" t="n">
-        <v>6.713751645293087e-05</v>
+        <v>4.170718881368884e-09</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0001095328989322297</v>
+        <v>2.041201208058396e-09</v>
       </c>
       <c r="GC8" t="n">
-        <v>7.69847902120091e-05</v>
+        <v>8.50489811909938e-09</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.00022449555399362</v>
+        <v>7.282000780151066e-09</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0002152900851797312</v>
+        <v>1.195906929041257e-09</v>
       </c>
       <c r="GF8" t="n">
-        <v>5.107062315801159e-05</v>
+        <v>6.497868909605131e-11</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0004163378325756639</v>
+        <v>9.697938008201845e-10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.717701952896888e-10</v>
+        <v>7.528392131916917e-09</v>
       </c>
       <c r="B9" t="n">
-        <v>2.929938236473362e-10</v>
+        <v>2.617080596678534e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.700439079103781e-11</v>
+        <v>1.963166518237358e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>3.999888198435997e-10</v>
+        <v>8.202834855808305e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>3.409078852545377e-10</v>
+        <v>3.241049206792468e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>9.105430298639305e-11</v>
+        <v>2.025675982508801e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.090616152417013e-10</v>
+        <v>3.831961414846319e-10</v>
       </c>
       <c r="H9" t="n">
-        <v>6.329556323514396e-11</v>
+        <v>5.65777868999362e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.064757310098585e-10</v>
+        <v>5.35122790523701e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>2.024690692881137e-10</v>
+        <v>5.421831872354232e-10</v>
       </c>
       <c r="K9" t="n">
-        <v>2.088098166597163e-10</v>
+        <v>3.114961799610683e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.549442155805551e-11</v>
+        <v>6.050738576846015e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.464912774418181e-10</v>
+        <v>1.664059467998413e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.78991393823469e-10</v>
+        <v>1.35965771974611e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.745296212580683e-10</v>
+        <v>2.19783764521253e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.393113207599384e-10</v>
+        <v>2.96283753087323e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.644480246421054e-10</v>
+        <v>8.749045932177069e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>1.089594525716109e-10</v>
+        <v>4.629092664742984e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>4.038636092218439e-11</v>
+        <v>3.738310550005508e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>7.398429091587388e-11</v>
+        <v>1.853028841480864e-11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.228015883425471e-10</v>
+        <v>3.803060533158487e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>2.571881770052631e-11</v>
+        <v>4.908860429253536e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>3.072899990019806e-10</v>
+        <v>3.323955999334771e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>9.716581012009229e-11</v>
+        <v>2.143719424196888e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.763370144347576e-10</v>
+        <v>4.234754324983214e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.2508900833258e-11</v>
+        <v>3.296918293926865e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.090015508409259e-10</v>
+        <v>1.44892897679938e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.319769790292696e-12</v>
+        <v>2.136984367240302e-09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.868769722301877e-10</v>
+        <v>6.863621671016062e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.102537713904006e-10</v>
+        <v>5.014663129188079e-10</v>
       </c>
       <c r="AE9" t="n">
-        <v>6.797017115811599e-11</v>
+        <v>5.06292430202393e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.276488498236361e-10</v>
+        <v>6.937927565786595e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.991176636026111e-11</v>
+        <v>1.111949288201686e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>9.650247267956047e-11</v>
+        <v>1.2911371971569e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>7.064401841283541e-11</v>
+        <v>1.478528499632148e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6.514939282498133e-11</v>
+        <v>1.108581004771736e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>8.208313195812167e-11</v>
+        <v>4.932612096553157e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.755916147014538e-11</v>
+        <v>3.891909905462398e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>8.704800075198804e-11</v>
+        <v>7.267101143071386e-09</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.451800650866588e-11</v>
+        <v>3.660058256471643e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.441770917405162e-11</v>
+        <v>2.092179762769319e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.746583764398849e-11</v>
+        <v>2.675899724025044e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.177188026559641e-11</v>
+        <v>3.165104622837589e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.278153693995421e-10</v>
+        <v>1.832387019895521e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.732935736719625e-11</v>
+        <v>3.610263421549575e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.558274591115463e-11</v>
+        <v>6.44260467197455e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.116798125673114e-10</v>
+        <v>2.191776360405129e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.575592946725159e-11</v>
+        <v>8.037730481191829e-09</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.479432492652478e-10</v>
+        <v>3.000502957206663e-09</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.879179947378745e-11</v>
+        <v>2.240545526888127e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.09376820101037e-10</v>
+        <v>1.943255867331573e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.006260518301218e-11</v>
+        <v>3.59844642972007e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.434202310887869e-11</v>
+        <v>3.752045785176961e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.198537764820713e-11</v>
+        <v>1.97683092117984e-09</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.906589189448198e-11</v>
+        <v>1.01213237790887e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.010487526986736e-11</v>
+        <v>4.15897449812519e-09</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.087109454324448e-11</v>
+        <v>3.028934436599684e-09</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.588365723670382e-11</v>
+        <v>9.027467662292565e-09</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.725320802365871e-10</v>
+        <v>8.477790025551712e-09</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.251970551847009e-11</v>
+        <v>3.59527785320779e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.936392961063518e-11</v>
+        <v>4.878335513325283e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.693676865421878e-10</v>
+        <v>1.127008797396911e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.679216984524118e-11</v>
+        <v>1.361253221254799e-09</v>
       </c>
       <c r="BL9" t="n">
-        <v>8.148431235310838e-11</v>
+        <v>5.166237437848054e-10</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.367244594791984e-11</v>
+        <v>6.001377617081971e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.670440076348648e-11</v>
+        <v>1.794070447758145e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.185055387153966e-10</v>
+        <v>1.988749165349191e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>6.412452513426814e-11</v>
+        <v>9.062032901852035e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.176428217677163e-11</v>
+        <v>1.220269885138237e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>4.642042999991602e-11</v>
+        <v>6.17512219136529e-09</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.120933554310533e-11</v>
+        <v>4.924557650554107e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.734656665148165e-11</v>
+        <v>3.912979273934525e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.933681166577106e-11</v>
+        <v>3.214125410266888e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.835782815848511e-11</v>
+        <v>6.890159998107492e-09</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.365132035191507e-10</v>
+        <v>4.361393468599317e-09</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.251212493671218e-11</v>
+        <v>4.928819574701038e-10</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.01096533658918e-11</v>
+        <v>3.108344026614418e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>7.803400980943564e-11</v>
+        <v>9.538202228043247e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.950571616679227e-11</v>
+        <v>5.700354410720365e-09</v>
       </c>
       <c r="CB9" t="n">
-        <v>1.130871177951187e-11</v>
+        <v>2.120987163678478e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.38954142531378e-11</v>
+        <v>4.578053491854917e-10</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.348198371859844e-11</v>
+        <v>9.793237748523254e-11</v>
       </c>
       <c r="CE9" t="n">
-        <v>6.521559681171851e-11</v>
+        <v>8.466471967949474e-09</v>
       </c>
       <c r="CF9" t="n">
-        <v>6.095345755907644e-11</v>
+        <v>9.65375210326691e-11</v>
       </c>
       <c r="CG9" t="n">
-        <v>1.105346977142707e-11</v>
+        <v>2.131359755352946e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>3.282945530008741e-12</v>
+        <v>2.67817723553776e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>4.766493102992264e-11</v>
+        <v>5.547669434946556e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.217179568940852e-11</v>
+        <v>4.732506608817744e-10</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.166018843978822e-11</v>
+        <v>2.127103826410348e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>8.829233177909401e-11</v>
+        <v>2.449197955556315e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>9.407608025924219e-11</v>
+        <v>4.552864751872221e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>3.612158835930579e-11</v>
+        <v>9.062407713145149e-09</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.871680935239262e-11</v>
+        <v>1.317437003933719e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>9.024746228103453e-11</v>
+        <v>7.808536928166632e-09</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.3422274403041e-10</v>
+        <v>3.712931295751787e-09</v>
       </c>
       <c r="CR9" t="n">
-        <v>2.038835940354478e-11</v>
+        <v>2.53441045927616e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.403376581610161e-10</v>
+        <v>2.095595474926881e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>1.396917217316718e-11</v>
+        <v>8.355404368387553e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.018911773871146e-11</v>
+        <v>5.03943864416101e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.569271795842653e-11</v>
+        <v>1.174204733445094e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>5.665267560628351e-11</v>
+        <v>8.000074380731803e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.492303916694198e-11</v>
+        <v>6.488205528398794e-10</v>
       </c>
       <c r="CY9" t="n">
-        <v>5.084035969993295e-11</v>
+        <v>3.462515607566274e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.763081868000338e-11</v>
+        <v>3.089822842028411e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>6.361917936903438e-11</v>
+        <v>6.597379087480704e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.040753156740127e-11</v>
+        <v>1.472128419166552e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.015250904179421e-11</v>
+        <v>1.640403923808265e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>7.628657427982688e-11</v>
+        <v>1.632306512178161e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.307222385893425e-10</v>
+        <v>5.886829357315548e-10</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.577272284476351e-10</v>
+        <v>4.127485575544654e-10</v>
       </c>
       <c r="DG9" t="n">
-        <v>7.138131752348897e-11</v>
+        <v>1.035206143029654e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>2.42267067518398e-10</v>
+        <v>2.072533034080948e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>3.811231330530518e-10</v>
+        <v>2.95872171207634e-09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>7.356598663577074e-11</v>
+        <v>9.083587215741318e-09</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.887542622203142e-10</v>
+        <v>2.481647332075454e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>3.081859212272775e-10</v>
+        <v>6.106007255368695e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>1.085223508279221e-10</v>
+        <v>2.120826403384513e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>7.232694998471345e-11</v>
+        <v>2.429019652083753e-09</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.23404150681661e-11</v>
+        <v>2.607277727051382e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>4.434129279029531e-12</v>
+        <v>2.248861097342569e-09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.599683996378332e-10</v>
+        <v>5.535165659154018e-10</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.835224854029871e-11</v>
+        <v>1.850162578698189e-09</v>
       </c>
       <c r="DS9" t="n">
-        <v>8.487946456803286e-11</v>
+        <v>6.857001633164828e-10</v>
       </c>
       <c r="DT9" t="n">
-        <v>1.043764553954052e-11</v>
+        <v>3.108314938771173e-09</v>
       </c>
       <c r="DU9" t="n">
-        <v>4.98771128565334e-11</v>
+        <v>8.238060900112032e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.183025066797683e-10</v>
+        <v>5.367287947422028e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>2.254286167457931e-11</v>
+        <v>2.488319772453451e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>6.469479119086685e-11</v>
+        <v>4.923852880978075e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.205344518113606e-10</v>
+        <v>5.379009238026811e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.978479012565426e-12</v>
+        <v>3.077156973674278e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>1.37083322124254e-11</v>
+        <v>2.655046626998114e-09</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.166829965981719e-10</v>
+        <v>4.18459489281986e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.953455973369156e-11</v>
+        <v>7.203986296389076e-10</v>
       </c>
       <c r="ED9" t="n">
-        <v>4.939934572512072e-11</v>
+        <v>1.079958167338191e-08</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.82900760509197e-11</v>
+        <v>4.110775275734113e-09</v>
       </c>
       <c r="EF9" t="n">
-        <v>3.45507303323167e-12</v>
+        <v>1.637078472782605e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>9.752337826185453e-11</v>
+        <v>2.780827124126972e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>8.113942157050857e-11</v>
+        <v>2.716882052666847e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>5.922710932804165e-11</v>
+        <v>5.537330594052037e-10</v>
       </c>
       <c r="EJ9" t="n">
-        <v>6.752436110257776e-11</v>
+        <v>2.434227486247664e-09</v>
       </c>
       <c r="EK9" t="n">
-        <v>7.347510794231127e-11</v>
+        <v>4.205875203666665e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.450970841896051e-11</v>
+        <v>2.170586599348212e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.078987680452892e-11</v>
+        <v>1.688773565433621e-10</v>
       </c>
       <c r="EN9" t="n">
-        <v>5.755026316611733e-11</v>
+        <v>2.891767381107968e-10</v>
       </c>
       <c r="EO9" t="n">
-        <v>1.997409182497023e-12</v>
+        <v>1.417111428203555e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>5.391489338313349e-11</v>
+        <v>3.09404812881553e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>7.849736138876295e-11</v>
+        <v>1.131545968036107e-10</v>
       </c>
       <c r="ER9" t="n">
-        <v>7.62956711697349e-12</v>
+        <v>7.107169297526639e-10</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.272490862680442e-10</v>
+        <v>1.467474364247323e-09</v>
       </c>
       <c r="ET9" t="n">
-        <v>5.528635882434685e-11</v>
+        <v>1.163225182843064e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>4.099939832080679e-11</v>
+        <v>3.030367345946416e-10</v>
       </c>
       <c r="EV9" t="n">
-        <v>2.291209305615993e-10</v>
+        <v>2.218220718219754e-09</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.603729384875741e-11</v>
+        <v>1.896512280552543e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>1.149869175570695e-11</v>
+        <v>1.408918121059699e-11</v>
       </c>
       <c r="EY9" t="n">
-        <v>4.974305689575687e-11</v>
+        <v>9.034943460051181e-09</v>
       </c>
       <c r="EZ9" t="n">
-        <v>3.640784895786453e-11</v>
+        <v>4.696267819070954e-10</v>
       </c>
       <c r="FA9" t="n">
-        <v>4.042150988925464e-11</v>
+        <v>3.963947392549017e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>2.339313118215891e-11</v>
+        <v>1.139034977448716e-09</v>
       </c>
       <c r="FC9" t="n">
-        <v>3.394110686949503e-11</v>
+        <v>4.218037918946038e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>2.104059634855382e-11</v>
+        <v>1.300375918056318e-10</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.484193670742151e-11</v>
+        <v>2.285844402649673e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>9.010039242474122e-11</v>
+        <v>3.440185913916594e-10</v>
       </c>
       <c r="FG9" t="n">
-        <v>2.958405395658836e-11</v>
+        <v>5.046586482038151e-10</v>
       </c>
       <c r="FH9" t="n">
-        <v>5.768849634102402e-11</v>
+        <v>6.030373977949921e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>2.126604448093872e-10</v>
+        <v>4.91510077083035e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>2.141907762265305e-10</v>
+        <v>4.956999255512073e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>8.604585099991624e-11</v>
+        <v>1.868987187236826e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>2.907732388202078e-11</v>
+        <v>7.348432973230956e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>7.539269555878469e-12</v>
+        <v>2.296971279847071e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.338677502182861e-10</v>
+        <v>3.034405615665037e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>1.151071390981251e-10</v>
+        <v>1.095537527362467e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>2.744591359737925e-11</v>
+        <v>6.025631549277932e-09</v>
       </c>
       <c r="FQ9" t="n">
-        <v>4.244593565516652e-11</v>
+        <v>1.147675732227071e-08</v>
       </c>
       <c r="FR9" t="n">
-        <v>1.55417206881836e-10</v>
+        <v>9.479379059484927e-09</v>
       </c>
       <c r="FS9" t="n">
-        <v>1.328813586942701e-10</v>
+        <v>3.979256368857875e-10</v>
       </c>
       <c r="FT9" t="n">
-        <v>9.812137907738716e-11</v>
+        <v>7.426284587275234e-10</v>
       </c>
       <c r="FU9" t="n">
-        <v>2.099993096082997e-11</v>
+        <v>1.16555409768182e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>5.610497136321335e-11</v>
+        <v>5.261151514446283e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>3.355560274087566e-11</v>
+        <v>9.349834684257985e-09</v>
       </c>
       <c r="FX9" t="n">
-        <v>3.177767771145312e-11</v>
+        <v>3.222972777550126e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>1.653040898608182e-10</v>
+        <v>2.098056839372475e-09</v>
       </c>
       <c r="FZ9" t="n">
-        <v>7.199957297032711e-11</v>
+        <v>1.26128785193913e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>6.997753071447121e-12</v>
+        <v>7.622179332145151e-09</v>
       </c>
       <c r="GB9" t="n">
-        <v>7.541503532770832e-11</v>
+        <v>1.469641852658299e-09</v>
       </c>
       <c r="GC9" t="n">
-        <v>1.960899359554347e-10</v>
+        <v>1.252727344080995e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>3.415711507040453e-12</v>
+        <v>1.034248509057534e-08</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.760297268533662e-10</v>
+        <v>3.172227591718979e-09</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.704594964126784e-11</v>
+        <v>1.078171441015741e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>9.180622928539606e-11</v>
+        <v>3.144334348448297e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0005437594372779131</v>
+        <v>2.176482848881278e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01948164589703083</v>
+        <v>0.0004715273098554462</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001295594498515129</v>
+        <v>0.0001774442789610475</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007465387228876352</v>
+        <v>0.0001894260349217802</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002245426876470447</v>
+        <v>0.0001178606180474162</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009139427915215492</v>
+        <v>0.0005408563883975148</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001598745933733881</v>
+        <v>4.974837065674365e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005721834488213062</v>
+        <v>0.0001412329147569835</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003125509014353156</v>
+        <v>0.0001423651119694114</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002785509219393134</v>
+        <v>0.0001076831467798911</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01762391999363899</v>
+        <v>0.0005438898224383593</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001915556495077908</v>
+        <v>0.0002392248425167054</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006247407291084528</v>
+        <v>0.0004107716376893222</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001284909376408905</v>
+        <v>3.551499685272574e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>0.007767750881612301</v>
+        <v>0.0006329325260594487</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005015545757487416</v>
+        <v>4.330620140535757e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005931388586759567</v>
+        <v>3.819986886810511e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003790396265685558</v>
+        <v>8.61567968968302e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001040843548253179</v>
+        <v>9.980625327443704e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001547596184536815</v>
+        <v>5.59236686967779e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0001311447704210877</v>
+        <v>1.576641807332635e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001492357579991221</v>
+        <v>4.182287739240564e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.003267225343734026</v>
+        <v>7.89607220212929e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.002309468807652593</v>
+        <v>0.0001042737058014609</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0006054706173017621</v>
+        <v>0.0001117061910917982</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00395846227183938</v>
+        <v>0.0001248551852768287</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.002893255092203617</v>
+        <v>5.876710201846436e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0008065177826210856</v>
+        <v>6.394994852598757e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0003967441152781248</v>
+        <v>1.453464210499078e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0008075012592598796</v>
+        <v>9.648242121329531e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0008939719991758466</v>
+        <v>0.0001254038652405143</v>
       </c>
       <c r="AF10" t="n">
-        <v>5.804811371490359e-05</v>
+        <v>0.0001354023406747729</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0008972235955297947</v>
+        <v>0.0001828322710935026</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0002722018689382821</v>
+        <v>3.881586599163711e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0004551914753392339</v>
+        <v>0.0003610445710364729</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0005107471370138228</v>
+        <v>4.874272053712048e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.000763239455409348</v>
+        <v>8.96373821888119e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.002803865587338805</v>
+        <v>6.301723624346778e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0004315804690122604</v>
+        <v>4.498056296142749e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00174347625579685</v>
+        <v>7.329622167162597e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0004134612972848117</v>
+        <v>5.848028376931325e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0023809471167624</v>
+        <v>0.0001028340484481305</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.000856453669257462</v>
+        <v>3.006876795552671e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001140867359936237</v>
+        <v>9.89841646514833e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.002045114059001207</v>
+        <v>1.226896074513206e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.002117503667250276</v>
+        <v>0.0001046104734996334</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01097353175282478</v>
+        <v>0.0003928011865355074</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0009329977910965681</v>
+        <v>0.0001532932801637799</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.002770890947431326</v>
+        <v>0.0001044921227730811</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0004904841771349311</v>
+        <v>0.0003012052911799401</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.005685090553015471</v>
+        <v>0.0004250380152370781</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.004755707923322916</v>
+        <v>2.277343810419552e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.002387858927249908</v>
+        <v>8.002719550859183e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.00399227486923337</v>
+        <v>1.246523606823757e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0008072585333138704</v>
+        <v>0.0001189149770652875</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00416128896176815</v>
+        <v>1.211586277349852e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.003806783584877849</v>
+        <v>0.000122271419968456</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.613948890939355e-05</v>
+        <v>0.0001326680649071932</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001522576319985092</v>
+        <v>0.0001653498911764473</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001418359111994505</v>
+        <v>2.32074180530617e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002505209296941757</v>
+        <v>3.87953914469108e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.002660064492374659</v>
+        <v>0.0002034170611295849</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.003414977341890335</v>
+        <v>7.621162512805313e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>5.731430428568274e-05</v>
+        <v>2.111623325617984e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.002128142397850752</v>
+        <v>0.0001425937807653099</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001990841701626778</v>
+        <v>5.041758049628697e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0004135955241508782</v>
+        <v>8.94553231773898e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.001344913500361145</v>
+        <v>9.210365533363074e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.749461706727743e-07</v>
+        <v>7.402434857795015e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.000975141185335815</v>
+        <v>8.881927351467311e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001306880731135607</v>
+        <v>7.728701166342944e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0002852262696251273</v>
+        <v>8.70426811161451e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.001188283320516348</v>
+        <v>7.236738747451454e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.007162912283092737</v>
+        <v>0.0001605419965926558</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001551072113215923</v>
+        <v>9.980089089367539e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.00136478862259537</v>
+        <v>1.492946466896683e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0004174812056589872</v>
+        <v>3.519477104418911e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002442259341478348</v>
+        <v>0.0002357902994845062</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0002399572404101491</v>
+        <v>0.0001753345859469846</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0002504309522919357</v>
+        <v>5.220920866122469e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.002561430912464857</v>
+        <v>8.678024460095912e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0001981302484637126</v>
+        <v>9.576129741617478e-06</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.003255100687965751</v>
+        <v>0.0001513840688858181</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001584302634000778</v>
+        <v>5.350410719984211e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0006653739837929606</v>
+        <v>4.120808443985879e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.000449057697551325</v>
+        <v>8.406386768911034e-06</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001233516377396882</v>
+        <v>0.000135511189000681</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001505811349488795</v>
+        <v>7.693344741710462e-06</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0009891523513942957</v>
+        <v>2.545902134443168e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001729588024318218</v>
+        <v>1.492589763074648e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.003864525351673365</v>
+        <v>5.759478517575189e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.00126612838357687</v>
+        <v>5.258751843939535e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>2.650129317771643e-05</v>
+        <v>0.000164101249538362</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.00499879801645875</v>
+        <v>0.0001175787838292308</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001701390603557229</v>
+        <v>1.575082023919094e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.002494193846359849</v>
+        <v>6.235426553757861e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.003778737969696522</v>
+        <v>0.0001617751986486837</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.003632978303357959</v>
+        <v>0.0002446705766487867</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0007802916807122529</v>
+        <v>7.718900451436639e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>9.411925566382706e-05</v>
+        <v>4.9428446800448e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.00321298441849649</v>
+        <v>0.0001304338511545211</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001644684700295329</v>
+        <v>7.539375656051561e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001654027262702584</v>
+        <v>6.398854020517319e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0006331672775559127</v>
+        <v>2.876295184250921e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.001007154118269682</v>
+        <v>0.0001707624469418079</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001411720528267324</v>
+        <v>2.734093141043559e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.001946404343470931</v>
+        <v>2.826523996191099e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.00142511329613626</v>
+        <v>2.428945481369738e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0008427157299593091</v>
+        <v>8.73727367434185e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.004048991482704878</v>
+        <v>0.0002161484298994765</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0005713548744097352</v>
+        <v>0.0001564650010550395</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.005096034146845341</v>
+        <v>0.0001084901305148378</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003602877492085099</v>
+        <v>4.858610918745399e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.007104035932570696</v>
+        <v>0.0001503434032201767</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0005553795490413904</v>
+        <v>2.336256329726893e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.00312126218341291</v>
+        <v>0.0001860741176642478</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.003108812496066093</v>
+        <v>0.000128479499835521</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0006242624949663877</v>
+        <v>4.924407039652579e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001558622112497687</v>
+        <v>0.0001115530030801892</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.00152816844638437</v>
+        <v>2.79864852927858e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0005834851763211191</v>
+        <v>0.0001154408455477096</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0006219659117050469</v>
+        <v>3.045328412554227e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002276551676914096</v>
+        <v>0.0001006788006634451</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.002984070451930165</v>
+        <v>0.0001052549632731825</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0008210767991840839</v>
+        <v>0.0001781482569640502</v>
       </c>
       <c r="DV10" t="n">
-        <v>3.091612597927451e-05</v>
+        <v>6.852005026303232e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.000385293154977262</v>
+        <v>3.157838364131749e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.002495004329830408</v>
+        <v>5.848007276654243e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0006182303186506033</v>
+        <v>0.0001680418790783733</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001161490217782557</v>
+        <v>1.073749444913119e-08</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001328627578914165</v>
+        <v>0.0001235012168763205</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001064674463123083</v>
+        <v>2.775475513772108e-05</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0006583775975741446</v>
+        <v>0.0001597501250216737</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0003877740236930549</v>
+        <v>0.0001508666755398735</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.004134985618293285</v>
+        <v>0.0002465878205839545</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.001191895105876029</v>
+        <v>1.398417771270033e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.003318991977721453</v>
+        <v>1.196349148813169e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001658407039940357</v>
+        <v>2.616221536300145e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0007453382131643593</v>
+        <v>5.05719544889871e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001018176088109612</v>
+        <v>8.92023672349751e-06</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001756893936544657</v>
+        <v>3.037003625649959e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001627509715035558</v>
+        <v>3.586721868487075e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003310015599709004</v>
+        <v>2.895788747991901e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0008539868285879493</v>
+        <v>0.0001129971351474524</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001202081912197173</v>
+        <v>4.440990960574709e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0023084816057235</v>
+        <v>0.0001092800157493912</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.001977961277589202</v>
+        <v>6.154640868771821e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.000987027189694345</v>
+        <v>0.0001156751022790559</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.002386213047429919</v>
+        <v>0.0001037669571815059</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001242951606400311</v>
+        <v>0.0001308639766648412</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004274999722838402</v>
+        <v>2.031691110460088e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.003652184037491679</v>
+        <v>9.886011866910849e-06</v>
       </c>
       <c r="EW10" t="n">
-        <v>8.492569031659514e-05</v>
+        <v>1.775119744706899e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0005253602284938097</v>
+        <v>3.534822462825105e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.00304592470638454</v>
+        <v>0.0001661568676354364</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001382906455546618</v>
+        <v>4.218082540319301e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0005876255454495549</v>
+        <v>8.102241554297507e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0004877387837041169</v>
+        <v>1.788033478078432e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0008585311588831246</v>
+        <v>0.000134228917886503</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.002494475804269314</v>
+        <v>1.581088872626424e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001621525269001722</v>
+        <v>2.076523014693521e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002051535062491894</v>
+        <v>5.177178900339641e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0009190283017233014</v>
+        <v>1.524151502962923e-05</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0009835816454142332</v>
+        <v>6.936551653780043e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001499736332334578</v>
+        <v>9.41245598369278e-05</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.002393063623458147</v>
+        <v>9.85268852673471e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0007792030810378492</v>
+        <v>2.975081588374451e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0001469500712119043</v>
+        <v>0.00021414301590994</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001528166932985187</v>
+        <v>4.359025115263648e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0009596754098311067</v>
+        <v>0.0001302062009926885</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0003100563189946115</v>
+        <v>0.0002730980340857059</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001727932598441839</v>
+        <v>0.0001276901311939582</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001222468446940184</v>
+        <v>0.0001162912813015282</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.004529111087322235</v>
+        <v>1.349329249933362e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.003116928972303867</v>
+        <v>8.25942333904095e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0008409902220591903</v>
+        <v>2.799447611323558e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001069480320438743</v>
+        <v>5.417778447736055e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.002054873388260603</v>
+        <v>0.000135616457555443</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.001261553610675037</v>
+        <v>0.0004339051083661616</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.002244528150185943</v>
+        <v>1.725102629279718e-05</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.002322398591786623</v>
+        <v>6.697927892673761e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0008363052038475871</v>
+        <v>7.607044244650751e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0009992518462240696</v>
+        <v>0.0002184547338401899</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0004833510611206293</v>
+        <v>4.445362719707191e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0005103247822262347</v>
+        <v>0.0003051490639336407</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0009484419715590775</v>
+        <v>0.0001249714259756729</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.00479845330119133</v>
+        <v>5.87558897677809e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.001028165919706225</v>
+        <v>0.0001002582721412182</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0005613301182165742</v>
+        <v>1.087026612367481e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.02308423258364201</v>
+        <v>0.0001379222376272082</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2700941860675812</v>
+        <v>0.00060332688735798</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0121845779940486</v>
+        <v>2.386633786954917e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1400018483400345</v>
+        <v>0.0002245729410788044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03652042523026466</v>
+        <v>5.665910430252552e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2636938095092773</v>
+        <v>0.0004183195997029543</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004772966727614403</v>
+        <v>8.532208448741585e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09588789939880371</v>
+        <v>6.466812192229554e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03361897543072701</v>
+        <v>2.750852218014188e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05820509791374207</v>
+        <v>5.813430470880121e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2540064752101898</v>
+        <v>0.0007246483583003283</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00303701451048255</v>
+        <v>7.536767225246876e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1028423234820366</v>
+        <v>0.0003814349474851042</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001460518687963486</v>
+        <v>0.0001224307052325457</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2426442503929138</v>
+        <v>0.0004337758291512728</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01864532195031643</v>
+        <v>1.376226464344654e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04840560629963875</v>
+        <v>8.486683509545401e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009806429035961628</v>
+        <v>7.047014514682814e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01251366175711155</v>
+        <v>3.325661236885935e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01337157469242811</v>
+        <v>9.048234642250463e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02460465952754021</v>
+        <v>1.873733708634973e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04296129196882248</v>
+        <v>4.147693834966049e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07205949723720551</v>
+        <v>3.375276355654933e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01753161661326885</v>
+        <v>7.472515426343307e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02438260987401009</v>
+        <v>4.785719283972867e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.06725317239761353</v>
+        <v>0.000193166866665706</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04252458363771439</v>
+        <v>5.251072252576705e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.005329102277755737</v>
+        <v>7.954739703563973e-05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01731729507446289</v>
+        <v>5.514948134077713e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.01848237402737141</v>
+        <v>2.650616079336032e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01523731276392937</v>
+        <v>0.0001455357414670289</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02967013418674469</v>
+        <v>7.519321661675349e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02477460727095604</v>
+        <v>0.0001449472911190242</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01395186129957438</v>
+        <v>6.234004104044288e-07</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.006000030785799026</v>
+        <v>0.0002691161644179374</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02479415200650692</v>
+        <v>4.488327977014706e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02446242980659008</v>
+        <v>0.0001086957345250994</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04352667927742004</v>
+        <v>6.493673572549596e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001667232252657413</v>
+        <v>5.82121720071882e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.006943641230463982</v>
+        <v>6.377438694471493e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001152393873780966</v>
+        <v>1.137665458372794e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.03269098326563835</v>
+        <v>1.580831667524762e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.002945689484477043</v>
+        <v>4.628689930541441e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0170839000493288</v>
+        <v>0.0001864376827143133</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02470722794532776</v>
+        <v>2.672809387149755e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.02915184944868088</v>
+        <v>0.0001250760979019105</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1975713521242142</v>
+        <v>0.0004507347766775638</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.001950948499143124</v>
+        <v>8.599760622018948e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.05770295858383179</v>
+        <v>0.0001190951152238995</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.02765282057225704</v>
+        <v>0.0002676100993994623</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1364703774452209</v>
+        <v>0.0002266863157274202</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.01165301818400621</v>
+        <v>1.267196239496116e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.02164324559271336</v>
+        <v>2.15978088817792e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0653376579284668</v>
+        <v>6.117662996985018e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.02452132478356361</v>
+        <v>7.299918797798455e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0472516342997551</v>
+        <v>8.508354949299246e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.06001319363713264</v>
+        <v>1.384667848469689e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.009381678886711597</v>
+        <v>0.000150211009895429</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.05216707661747932</v>
+        <v>9.513106488157064e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.08037464320659637</v>
+        <v>9.948742808774114e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01857436820864677</v>
+        <v>3.327930244267918e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.01689907163381577</v>
+        <v>0.0001095314437407069</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.001865943893790245</v>
+        <v>6.083115295041353e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.001097093801945448</v>
+        <v>3.787861351156607e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07127029448747635</v>
+        <v>8.217164577217773e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.01000308804214001</v>
+        <v>4.475213427213021e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.02312815375626087</v>
+        <v>9.329060412710533e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.006425327155739069</v>
+        <v>6.112373375799507e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.00216773385182023</v>
+        <v>2.496818706276827e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01239768415689468</v>
+        <v>0.0001634231593925506</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.00272298650816083</v>
+        <v>2.066748129436746e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.004344434011727571</v>
+        <v>0.0001061266957549378</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.01975430175662041</v>
+        <v>5.948857142357156e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1018017828464508</v>
+        <v>0.0002492911298759282</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0128833893686533</v>
+        <v>5.385172698879614e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.05302686616778374</v>
+        <v>9.010566282086074e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.02663053944706917</v>
+        <v>7.596390787512064e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.05129071325063705</v>
+        <v>0.0001514065079391003</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.01684296317398548</v>
+        <v>5.649985541822389e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0006298068910837173</v>
+        <v>3.679845394799486e-05</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.04623309522867203</v>
+        <v>6.286385178100318e-05</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.004180599004030228</v>
+        <v>2.518339897505939e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.03300882875919342</v>
+        <v>0.0001712415687507018</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0277280043810606</v>
+        <v>5.362235970096663e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02199049666523933</v>
+        <v>6.68250722810626e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.003947626799345016</v>
+        <v>3.641784132923931e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.04461454972624779</v>
+        <v>0.0001124971167882904</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.01749347895383835</v>
+        <v>3.280120290583e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.01310320012271404</v>
+        <v>2.101906648022123e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.02309484034776688</v>
+        <v>4.904096203972585e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.05126170441508293</v>
+        <v>2.490686347300652e-05</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005598020739853382</v>
+        <v>0.0001243765582330525</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.006117299664765596</v>
+        <v>0.0001451606367481872</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01507003419101238</v>
+        <v>0.0001890704588731751</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01949442736804485</v>
+        <v>3.120230758213438e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.003078053239732981</v>
+        <v>9.869636414805427e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.05300744995474815</v>
+        <v>1.534580587758683e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.05403919517993927</v>
+        <v>0.0001457267353544012</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.005935311317443848</v>
+        <v>5.162079833098687e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002167431637644768</v>
+        <v>3.56194723281078e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.02796841599047184</v>
+        <v>0.0001706971816020086</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.02205833047628403</v>
+        <v>5.19216300745029e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.03464195877313614</v>
+        <v>9.095513087231666e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.005702638067305088</v>
+        <v>9.542392945149913e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04850707203149796</v>
+        <v>0.0001289973297389224</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01737946271896362</v>
+        <v>8.475824870401993e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.02640135586261749</v>
+        <v>2.865522583306301e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.008576655760407448</v>
+        <v>4.213574720779434e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.005576861556619406</v>
+        <v>4.155690839979798e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.009329527616500854</v>
+        <v>0.0001706390321487561</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.008913579396903515</v>
+        <v>3.108791133854538e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1084200292825699</v>
+        <v>2.103563565469813e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03606671094894409</v>
+        <v>0.0002405786653980613</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.002494313754141331</v>
+        <v>0.0001304246834479272</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.005248419940471649</v>
+        <v>7.863876817282289e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.03802705556154251</v>
+        <v>3.175515303155407e-06</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01558523345738649</v>
+        <v>2.187007339671254e-07</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.005589612759649754</v>
+        <v>3.75410781998653e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.007432531099766493</v>
+        <v>0.0001042774820234627</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.01535838469862938</v>
+        <v>5.361764124245383e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.002569898962974548</v>
+        <v>8.243765478255227e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01032143458724022</v>
+        <v>4.309947689762339e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.004753006622195244</v>
+        <v>4.314210673328489e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.02424870431423187</v>
+        <v>7.904272933956236e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0107392119243741</v>
+        <v>0.000167968450114131</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03175603970885277</v>
+        <v>6.320500688161701e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.002269883640110493</v>
+        <v>3.931413448299281e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02471088618040085</v>
+        <v>8.240250281232875e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.02203634567558765</v>
+        <v>6.83101243339479e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.002790269441902637</v>
+        <v>8.871954923961312e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0009887428022921085</v>
+        <v>0.0001355179265374318</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01825403608381748</v>
+        <v>2.874599158531055e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.002931427676230669</v>
+        <v>6.502319592982531e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.01158789545297623</v>
+        <v>8.445711864624172e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0023620689753443</v>
+        <v>9.713500912766904e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01429750118404627</v>
+        <v>8.257808985945303e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03707843646407127</v>
+        <v>7.280324643943459e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01671922020614147</v>
+        <v>1.393225829815492e-06</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.007259863428771496</v>
+        <v>1.371270627714694e-06</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002123698126524687</v>
+        <v>1.435308149666525e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.04727816581726074</v>
+        <v>3.115346044069156e-05</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01379426103085279</v>
+        <v>1.928487108671106e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.006734445225447416</v>
+        <v>1.246563169843284e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01293251849710941</v>
+        <v>2.480787770764437e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.005293264053761959</v>
+        <v>2.611778108985163e-05</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01254746876657009</v>
+        <v>6.192229920998216e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01478577218949795</v>
+        <v>8.711525879334658e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0212175901979208</v>
+        <v>7.656376692466438e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.009346412494778633</v>
+        <v>7.212260970845819e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.04084492847323418</v>
+        <v>9.845624299487099e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.031680628657341</v>
+        <v>2.897000013035722e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.07610173523426056</v>
+        <v>6.618309998884797e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.01037327572703362</v>
+        <v>6.306174327619374e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.002322782995179296</v>
+        <v>2.325326386198867e-05</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.02568789012730122</v>
+        <v>0.0001945614203577861</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.01824776083230972</v>
+        <v>4.161739707342349e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03007044643163681</v>
+        <v>0.0001102497626561671</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001091984333470464</v>
+        <v>4.156550130574033e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0403733029961586</v>
+        <v>9.76937371888198e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.02913432754576206</v>
+        <v>2.757054244284518e-05</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.01410173624753952</v>
+        <v>2.503965515643358e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.02204821072518826</v>
+        <v>2.014311940001789e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01217825710773468</v>
+        <v>3.408066913834773e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0006711384048685431</v>
+        <v>0.0002240671310573816</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.009708542376756668</v>
+        <v>0.0001017417016555555</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.04318524897098541</v>
+        <v>0.0001756510027917102</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01101253926753998</v>
+        <v>0.0001276210095966235</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02679337002336979</v>
+        <v>0.0001539119111839682</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.008857926353812218</v>
+        <v>1.320474530075444e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.02129599824547768</v>
+        <v>9.878941636998206e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01910114102065563</v>
+        <v>8.907033770810813e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01442377828061581</v>
+        <v>3.210777140338905e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.05279998481273651</v>
+        <v>6.393679359462112e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.03885854780673981</v>
+        <v>9.310065797762945e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02426140382885933</v>
+        <v>0.0001375442370772362</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01370736956596375</v>
+        <v>0.0001021385687636212</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008922290056943893</v>
+        <v>6.593899161089212e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.02142512053251266</v>
+        <v>5.370668441173621e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.003675260348245502</v>
+        <v>4.600562897394411e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01859917491674423</v>
+        <v>1.418718602508307e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.04650051146745682</v>
+        <v>0.0001490455470047891</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.01996774598956108</v>
+        <v>3.463673056103289e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.03209981322288513</v>
+        <v>0.0002752907166723162</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.01183719653636217</v>
+        <v>1.038084519677795e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.02790356427431107</v>
+        <v>0.0002713850990403444</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.01698098331689835</v>
+        <v>0.0001446290261810645</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1272857487201691</v>
+        <v>3.438871135585941e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001055099070072174</v>
+        <v>3.097085209446959e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.005722253583371639</v>
+        <v>3.402948277653195e-05</v>
       </c>
     </row>
     <row r="12">
@@ -7827,1140 +7827,1140 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0001625073055038229</v>
+        <v>2.030251522455728e-10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003670740406960249</v>
+        <v>3.950492910576031e-08</v>
       </c>
       <c r="C14" t="n">
-        <v>6.533721898449585e-05</v>
+        <v>3.046680063789609e-08</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009331564069725573</v>
+        <v>9.303640524649381e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001097588567063212</v>
+        <v>7.124146828019207e-10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001307672588154674</v>
+        <v>1.943373639790025e-08</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004255551612004638</v>
+        <v>7.302858762159303e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005912304040975869</v>
+        <v>2.739471050006159e-08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00065939238993451</v>
+        <v>2.764710593794462e-08</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002234159910585731</v>
+        <v>1.713171826622784e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>0.003435318591073155</v>
+        <v>4.346865267734756e-08</v>
       </c>
       <c r="L14" t="n">
-        <v>7.02252727933228e-05</v>
+        <v>3.473166998446686e-08</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004990622983314097</v>
+        <v>1.130852567143847e-08</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0002625968481879681</v>
+        <v>1.333903743017117e-08</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001154388766735792</v>
+        <v>1.513963887589398e-08</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0002413186739431694</v>
+        <v>5.129834335093619e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001780540042091161</v>
+        <v>1.411878702839431e-08</v>
       </c>
       <c r="R14" t="n">
-        <v>0.000681525852996856</v>
+        <v>3.386895652823796e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000188314777915366</v>
+        <v>1.559517492921714e-08</v>
       </c>
       <c r="T14" t="n">
-        <v>0.00041594059439376</v>
+        <v>2.698130252554165e-08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.658635457919445e-05</v>
+        <v>8.700066445044286e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002292959106853232</v>
+        <v>1.439983776663212e-08</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0003594657173380256</v>
+        <v>5.157219540308233e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0001808006782084703</v>
+        <v>5.194793484264437e-10</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.908408249728382e-05</v>
+        <v>1.976443897433455e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000536738836672157</v>
+        <v>1.009973527033026e-08</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002643791376613081</v>
+        <v>1.779901559473274e-08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0002589089854154736</v>
+        <v>2.550426358993718e-08</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0001823353377403691</v>
+        <v>5.74426284316587e-09</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001477868936490268</v>
+        <v>2.033282697766481e-08</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0001958820794243366</v>
+        <v>9.136059908598781e-09</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.366581950103864e-05</v>
+        <v>3.386417368744787e-09</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.626610411331058e-05</v>
+        <v>1.540501948227302e-08</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.015810115262866e-05</v>
+        <v>8.951936969481267e-09</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.627723733894527e-05</v>
+        <v>2.399347565074095e-08</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.000165001314599067</v>
+        <v>2.7566601445983e-08</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0005129930796101689</v>
+        <v>1.486855438770363e-08</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0004245954041834921</v>
+        <v>2.090404116472655e-08</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001317017304245383</v>
+        <v>2.408064858627768e-08</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.00026314752176404</v>
+        <v>2.128249354527156e-09</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.000236154068261385</v>
+        <v>8.489512204334915e-09</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0003279149241279811</v>
+        <v>9.373423814906801e-09</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0002231803664471954</v>
+        <v>4.882160453689721e-09</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.97034551599063e-05</v>
+        <v>3.765283640433381e-09</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0002602206950541586</v>
+        <v>4.844596279696134e-09</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0002756398171186447</v>
+        <v>1.851344855197112e-08</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.002395435236394405</v>
+        <v>2.205485749584568e-08</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0004316969425417483</v>
+        <v>1.149877881800876e-08</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.445483788615093e-05</v>
+        <v>1.947604744145792e-09</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.692317351233214e-05</v>
+        <v>2.436651769244236e-08</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0003603432851377875</v>
+        <v>1.266818983047813e-09</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0006580305634997785</v>
+        <v>3.67835584214049e-09</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.000418921816162765</v>
+        <v>3.467373721477429e-09</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0002177967253373936</v>
+        <v>1.269310523355216e-08</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0001899121562018991</v>
+        <v>4.434961908827972e-08</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0005346187390387058</v>
+        <v>6.028759713672116e-08</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0005369714926928282</v>
+        <v>1.375388780644471e-08</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.533456614008173e-05</v>
+        <v>1.116099213049893e-08</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0009622533107176423</v>
+        <v>4.531333885893218e-08</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.000657912518363446</v>
+        <v>1.481341493914101e-09</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0001465335371904075</v>
+        <v>1.115594727707503e-08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0003492776013445109</v>
+        <v>3.351025412712261e-08</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0005166225600987673</v>
+        <v>7.22811819287017e-08</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001288246130570769</v>
+        <v>6.377255612477484e-09</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0004360439488664269</v>
+        <v>1.140568173241263e-08</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.339325333712623e-05</v>
+        <v>1.172163610618782e-08</v>
       </c>
       <c r="BO14" t="n">
-        <v>9.29082598304376e-05</v>
+        <v>5.946507730669737e-10</v>
       </c>
       <c r="BP14" t="n">
-        <v>8.740630437387154e-05</v>
+        <v>4.941675513236987e-09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001695942773949355</v>
+        <v>8.480824043033408e-09</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0002502007118891925</v>
+        <v>1.050726083917652e-08</v>
       </c>
       <c r="BS14" t="n">
-        <v>5.276987212710083e-05</v>
+        <v>1.416623707228837e-08</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0001371926628053188</v>
+        <v>1.077951772288088e-08</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.089000529143959e-05</v>
+        <v>2.501766438456343e-08</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.001302944030612707</v>
+        <v>2.152306421976391e-08</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0001800228492356837</v>
+        <v>5.000477365513234e-09</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0002044078282779083</v>
+        <v>2.597047465968672e-09</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0001010378473438323</v>
+        <v>3.395038694620212e-09</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001814131246646866</v>
+        <v>3.571891893372481e-09</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001317189598921686</v>
+        <v>2.879022797941388e-09</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.511259173043072e-05</v>
+        <v>1.852229036813924e-09</v>
       </c>
       <c r="CC14" t="n">
-        <v>7.095192995620891e-05</v>
+        <v>5.765140365099342e-09</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001724522007862106</v>
+        <v>3.087699873560723e-09</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.000619681435637176</v>
+        <v>1.258426918226974e-09</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001032346626743674</v>
+        <v>4.240699347235477e-09</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001043530501192436</v>
+        <v>3.609515797364793e-09</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001148991723312065</v>
+        <v>3.280193894283912e-09</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001485629036324099</v>
+        <v>7.616643316055161e-09</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0002266421215608716</v>
+        <v>4.063967828926707e-09</v>
       </c>
       <c r="CK14" t="n">
-        <v>7.059287599986419e-05</v>
+        <v>3.055255159978287e-09</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0001690173521637917</v>
+        <v>2.242160235255142e-09</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0008805063553154469</v>
+        <v>1.143378014489826e-08</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0001358927838737145</v>
+        <v>1.02522728084864e-08</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001872565189842135</v>
+        <v>2.497306894611029e-08</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001095279818400741</v>
+        <v>2.493849571294504e-08</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0005429125158116221</v>
+        <v>3.552477068069493e-08</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0007014228613115847</v>
+        <v>9.302812742362221e-09</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0006165137747302651</v>
+        <v>2.561841405679388e-09</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0003684494295157492</v>
+        <v>7.609652463713701e-09</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0003251582093071193</v>
+        <v>2.42979183440184e-08</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0001656257372815162</v>
+        <v>2.057261028198809e-09</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0005676117725670338</v>
+        <v>6.115013828633664e-09</v>
       </c>
       <c r="CX14" t="n">
-        <v>9.615143062546849e-05</v>
+        <v>3.389895031347123e-09</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0002930252230726182</v>
+        <v>3.420055127989485e-09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001352988183498383</v>
+        <v>3.661965397583344e-09</v>
       </c>
       <c r="DA14" t="n">
-        <v>7.947250560391694e-05</v>
+        <v>5.698228999762023e-09</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002206504868809134</v>
+        <v>1.975438479462355e-09</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001799060119083151</v>
+        <v>3.230793410580191e-10</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001723882887745276</v>
+        <v>4.096753603022307e-09</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0002806545817293227</v>
+        <v>8.900656212063041e-09</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.000551530160009861</v>
+        <v>3.965097050695476e-08</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001470568822696805</v>
+        <v>4.137658038416703e-08</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0005524563021026552</v>
+        <v>8.282388108682426e-09</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001231647795066237</v>
+        <v>1.33569599825023e-08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.001186374807730317</v>
+        <v>1.384858716590998e-08</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0001345831406069919</v>
+        <v>1.610623812098311e-08</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0002396773343207315</v>
+        <v>3.274387649909727e-09</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0008612981182523072</v>
+        <v>5.06603337058209e-09</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0002336816105525941</v>
+        <v>3.077517618521597e-08</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001059314017766155</v>
+        <v>3.074674026493085e-08</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0002681733458302915</v>
+        <v>1.286779038878194e-08</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004239326517563313</v>
+        <v>8.330169443127033e-09</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0001678353291936219</v>
+        <v>1.506101199311161e-08</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0004054759338032454</v>
+        <v>2.119612485529387e-09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0003566736704669893</v>
+        <v>1.046543829374968e-08</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.000307325943140313</v>
+        <v>1.172905150781389e-08</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0002277263847645372</v>
+        <v>4.123501096131577e-09</v>
       </c>
       <c r="DW14" t="n">
-        <v>8.48897616378963e-05</v>
+        <v>1.205712951701798e-08</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0004221591807436198</v>
+        <v>2.625244022169682e-09</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0001742387830745429</v>
+        <v>2.853150604664734e-09</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0004962297971360385</v>
+        <v>5.481942899621117e-09</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003069161321036518</v>
+        <v>4.493176319897429e-08</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0001505095133325085</v>
+        <v>1.590006348806128e-08</v>
       </c>
       <c r="EC14" t="n">
-        <v>7.643689605174586e-05</v>
+        <v>2.518347841373725e-08</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0003267455904278904</v>
+        <v>2.636901363928246e-09</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0007616282673552632</v>
+        <v>1.092618795439648e-08</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0005612136446870863</v>
+        <v>4.12322309628621e-09</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0008951883064582944</v>
+        <v>9.146780222124562e-09</v>
       </c>
       <c r="EH14" t="n">
-        <v>6.432541704270989e-05</v>
+        <v>2.198322857083213e-09</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001813791604945436</v>
+        <v>7.482812591774746e-09</v>
       </c>
       <c r="EJ14" t="n">
-        <v>9.435112588107586e-05</v>
+        <v>8.518672878210509e-09</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0003271212626714259</v>
+        <v>1.214474920629982e-08</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0003212945302948356</v>
+        <v>5.059634489157361e-09</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0001746903581079096</v>
+        <v>4.89309437412544e-09</v>
       </c>
       <c r="EN14" t="n">
-        <v>5.940150003880262e-05</v>
+        <v>1.3412427612991e-08</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0002581137814559042</v>
+        <v>1.592377607551043e-08</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0003381170681677759</v>
+        <v>1.111801317676964e-08</v>
       </c>
       <c r="EQ14" t="n">
-        <v>8.285448711831123e-05</v>
+        <v>8.394271944212051e-09</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.000418306648498401</v>
+        <v>8.386033201190912e-09</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0002797093475237489</v>
+        <v>5.662646351822787e-09</v>
       </c>
       <c r="ET14" t="n">
-        <v>4.762167372973636e-05</v>
+        <v>2.762393425115306e-09</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0005885777645744383</v>
+        <v>5.459663388052149e-09</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0004540204245131463</v>
+        <v>1.30800845710155e-08</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0001851621636888012</v>
+        <v>7.279845615215663e-09</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.000229274810408242</v>
+        <v>2.30703056658399e-09</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0005826235865242779</v>
+        <v>7.940622381852336e-09</v>
       </c>
       <c r="EZ14" t="n">
-        <v>3.88164771720767e-05</v>
+        <v>1.866501175840085e-09</v>
       </c>
       <c r="FA14" t="n">
-        <v>1.325404082308523e-05</v>
+        <v>1.433976493103728e-09</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.000108859094325453</v>
+        <v>4.976866696537741e-10</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0001204452273668721</v>
+        <v>8.476191304396252e-09</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0003317566006444395</v>
+        <v>7.64401075770138e-09</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0001440963242202997</v>
+        <v>5.808615810565243e-09</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002812842139974236</v>
+        <v>6.000974384079427e-09</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001144496854976751</v>
+        <v>1.735445565032023e-09</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0002643500629346818</v>
+        <v>7.75365904814862e-09</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0003253495669923723</v>
+        <v>2.763906081781897e-08</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0005794989410787821</v>
+        <v>1.122195847358398e-08</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0002302719076396897</v>
+        <v>2.870169879543027e-08</v>
       </c>
       <c r="FL14" t="n">
-        <v>6.936895078979433e-05</v>
+        <v>1.016916773011189e-08</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0001722056185826659</v>
+        <v>1.373377078728311e-09</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0001363222399959341</v>
+        <v>2.676056531925042e-08</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0002502445131540298</v>
+        <v>1.69878866529416e-08</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0006497618742287159</v>
+        <v>3.459157582597072e-08</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0002649548696354032</v>
+        <v>3.135189530212301e-08</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0003005223697982728</v>
+        <v>3.094334388720199e-08</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.000502966227941215</v>
+        <v>6.289870668751973e-08</v>
       </c>
       <c r="FT14" t="n">
-        <v>9.294912160839885e-05</v>
+        <v>6.899752769129464e-09</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0002811792655847967</v>
+        <v>1.902777047035897e-09</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001041432988131419</v>
+        <v>7.005019675432322e-09</v>
       </c>
       <c r="FW14" t="n">
-        <v>2.798574132611975e-05</v>
+        <v>3.680978366560339e-08</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002305346424691379</v>
+        <v>6.239942340613425e-09</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.000729277147911489</v>
+        <v>1.159303675279943e-08</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001017888644128107</v>
+        <v>2.085360506498546e-08</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0001959515066118911</v>
+        <v>1.850755637633483e-08</v>
       </c>
       <c r="GB14" t="n">
-        <v>1.62962078320561e-05</v>
+        <v>2.005306143360031e-08</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.000156287889694795</v>
+        <v>1.329558241280893e-08</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0003006122133228928</v>
+        <v>1.648277425658762e-08</v>
       </c>
       <c r="GE14" t="n">
-        <v>8.680026076035574e-05</v>
+        <v>1.542491290251746e-08</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0002097943070111796</v>
+        <v>4.034950151776684e-09</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0002751450520008802</v>
+        <v>3.066126463835417e-09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.180318832397461</v>
+        <v>0.5848846435546875</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2624476253986359</v>
+        <v>0.07003936171531677</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03602723777294159</v>
+        <v>1.371728539466858</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2170795798301697</v>
+        <v>0.5881034731864929</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1146289333701134</v>
+        <v>0.619350790977478</v>
       </c>
       <c r="F15" t="n">
-        <v>0.824756920337677</v>
+        <v>1.483222246170044</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2843971848487854</v>
+        <v>0.2449263781309128</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2468066364526749</v>
+        <v>0.7028997540473938</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1478591710329056</v>
+        <v>0.651999831199646</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8320124745368958</v>
+        <v>0.5539077520370483</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2442663460969925</v>
+        <v>0.2859893143177032</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08131936937570572</v>
+        <v>1.813968658447266</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1893030107021332</v>
+        <v>0.2350879311561584</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1216944605112076</v>
+        <v>1.163515090942383</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7159577012062073</v>
+        <v>2.460204839706421</v>
       </c>
       <c r="P15" t="n">
-        <v>0.517544150352478</v>
+        <v>0.2104295790195465</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.345853716135025</v>
+        <v>0.5330830216407776</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05499375611543655</v>
+        <v>1.027936577796936</v>
       </c>
       <c r="S15" t="n">
-        <v>0.122728168964386</v>
+        <v>0.1049882024526596</v>
       </c>
       <c r="T15" t="n">
-        <v>0.301302045583725</v>
+        <v>0.4458854794502258</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08859209716320038</v>
+        <v>0.5477308034896851</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1868656277656555</v>
+        <v>0.002783045172691345</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4058549702167511</v>
+        <v>0.204473152756691</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1560489535331726</v>
+        <v>0.1213886588811874</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.210093691945076</v>
+        <v>0.4285227060317993</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1270359307527542</v>
+        <v>0.1756923645734787</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01843433082103729</v>
+        <v>0.1334753036499023</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2663926184177399</v>
+        <v>0.2844670414924622</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1188983246684074</v>
+        <v>0.06491955369710922</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.149054080247879</v>
+        <v>0.4080002307891846</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0740465372800827</v>
+        <v>0.1097308173775673</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1120143160223961</v>
+        <v>0.125984251499176</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1418112367391586</v>
+        <v>0.5366302132606506</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.05035024881362915</v>
+        <v>0.2583291232585907</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.05687310546636581</v>
+        <v>0.1343338936567307</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.03541107103228569</v>
+        <v>0.6521579027175903</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.2485543936491013</v>
+        <v>0.1930579245090485</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.1174021139740944</v>
+        <v>0.05275344848632812</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.1018578112125397</v>
+        <v>0.2655395567417145</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.18299899995327</v>
+        <v>0.4317006468772888</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.03424657136201859</v>
+        <v>0.7594559788703918</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.05385412648320198</v>
+        <v>0.07194268703460693</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.03006621822714806</v>
+        <v>0.1531426310539246</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.141258493065834</v>
+        <v>0.1867043524980545</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.01079247612506151</v>
+        <v>0.03339933976531029</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.7277436852455139</v>
+        <v>0.08120882511138916</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2824447453022003</v>
+        <v>0.8813360929489136</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1099474802613258</v>
+        <v>0.7129140496253967</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1571962535381317</v>
+        <v>0.1728441119194031</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.5958960652351379</v>
+        <v>0.4892546236515045</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.6714555621147156</v>
+        <v>1.582449555397034</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.05543580651283264</v>
+        <v>0.468798041343689</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.353589653968811</v>
+        <v>0.3306079208850861</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1189827397465706</v>
+        <v>0.1486810296773911</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.2096754014492035</v>
+        <v>0.307512104511261</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.4472244381904602</v>
+        <v>0.4695419073104858</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.1104241758584976</v>
+        <v>0.2256154716014862</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.165772870182991</v>
+        <v>0.09923109412193298</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.05268099904060364</v>
+        <v>1.17997670173645</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.03570632264018059</v>
+        <v>0.768659770488739</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.3716038465499878</v>
+        <v>0.0421411320567131</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1683153361082077</v>
+        <v>0.1908360570669174</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.04659848660230637</v>
+        <v>0.2998316884040833</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.02140155807137489</v>
+        <v>0.5671635866165161</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.2061213105916977</v>
+        <v>0.2433558851480484</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.05190711468458176</v>
+        <v>0.8958279490470886</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.2324418872594833</v>
+        <v>0.006030023097991943</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1896874457597733</v>
+        <v>0.06480519473552704</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1815392524003983</v>
+        <v>0.1017649248242378</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1858390867710114</v>
+        <v>0.1734987199306488</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.1701963841915131</v>
+        <v>0.1747335642576218</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.1692915707826614</v>
+        <v>0.2440392822027206</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.3561715483665466</v>
+        <v>0.07315399497747421</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2577700614929199</v>
+        <v>0.1201103627681732</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.105206161737442</v>
+        <v>0.6262916922569275</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.1410582214593887</v>
+        <v>0.6708921194076538</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.387031614780426</v>
+        <v>0.1901224702596664</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.4585424661636353</v>
+        <v>0.7034153342247009</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.05101502686738968</v>
+        <v>0.3462085425853729</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.2427727282047272</v>
+        <v>0.1112069487571716</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0170366894453764</v>
+        <v>0.07022160291671753</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.2071567475795746</v>
+        <v>0.07287240028381348</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.2340685129165649</v>
+        <v>0.05601990222930908</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.009120514616370201</v>
+        <v>0.5408768057823181</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0006161481142044067</v>
+        <v>0.1264802813529968</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.08329862356185913</v>
+        <v>0.1124960035085678</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.1400411128997803</v>
+        <v>0.1481123417615891</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.02694472298026085</v>
+        <v>0.1375765800476074</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.2237138301134109</v>
+        <v>0.08195298910140991</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0202200785279274</v>
+        <v>0.08892946690320969</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.03247847408056259</v>
+        <v>0.1525468230247498</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.06939671188592911</v>
+        <v>0.09991998225450516</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.004537966102361679</v>
+        <v>0.2370522916316986</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.006920285522937775</v>
+        <v>0.1604753881692886</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.625977098941803</v>
+        <v>0.292252391576767</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.1016014590859413</v>
+        <v>0.5923437476158142</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.08734869211912155</v>
+        <v>0.461259514093399</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.04722239077091217</v>
+        <v>0.1652331799268723</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.02921108342707157</v>
+        <v>0.03871528059244156</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.1915698796510696</v>
+        <v>0.1025032475590706</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.2226179391145706</v>
+        <v>0.1166781410574913</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.01289805956184864</v>
+        <v>0.5053735375404358</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.02510286867618561</v>
+        <v>0.1047535911202431</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.07357688993215561</v>
+        <v>0.3172684907913208</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.1475271880626678</v>
+        <v>0.3495361804962158</v>
       </c>
       <c r="DB15" t="n">
-        <v>6.191432476043701e-06</v>
+        <v>0.144146203994751</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.2236250042915344</v>
+        <v>0.0201024953275919</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.03981001675128937</v>
+        <v>0.0994885042309761</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08251099288463593</v>
+        <v>0.1424831300973892</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.109473742544651</v>
+        <v>0.1321528553962708</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.04461254179477692</v>
+        <v>0.6422188878059387</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.1613059341907501</v>
+        <v>0.2733647227287292</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.3635796308517456</v>
+        <v>0.1941564381122589</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.002030434086918831</v>
+        <v>0.262524276971817</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.07045847177505493</v>
+        <v>0.432799905538559</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2261217683553696</v>
+        <v>0.2326010167598724</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.1083736270666122</v>
+        <v>0.5219295620918274</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.1072840914130211</v>
+        <v>0.02204790152609348</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.008241094648838043</v>
+        <v>0.1793106496334076</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1055444628000259</v>
+        <v>0.6419658064842224</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0298868790268898</v>
+        <v>0.07922375947237015</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.04442330077290535</v>
+        <v>0.3435224592685699</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1124017238616943</v>
+        <v>0.4133778810501099</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1855147331953049</v>
+        <v>0.2228248417377472</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.4045686423778534</v>
+        <v>0.2385864108800888</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.04623319208621979</v>
+        <v>0.4878709316253662</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.01469737198203802</v>
+        <v>0.1388528794050217</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.1713905185461044</v>
+        <v>0.515184223651886</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.02710531279444695</v>
+        <v>0.6427204608917236</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.03964009135961533</v>
+        <v>0.7106972336769104</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02378075942397118</v>
+        <v>0.2253076732158661</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.3302265703678131</v>
+        <v>0.5810720920562744</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.02017518505454063</v>
+        <v>0.1263360679149628</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.02929426357150078</v>
+        <v>0.2373557835817337</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.125989094376564</v>
+        <v>0.1232561841607094</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.1558857858181</v>
+        <v>0.1578329056501389</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.165084645152092</v>
+        <v>0.1415406912565231</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.02859915792942047</v>
+        <v>0.4527249932289124</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.07607606053352356</v>
+        <v>0.004408175125718117</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01644260250031948</v>
+        <v>0.4152713418006897</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.02583561837673187</v>
+        <v>0.1092369481921196</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.009257040917873383</v>
+        <v>0.01152574829757214</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.03606799617409706</v>
+        <v>0.02155927568674088</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.04177474975585938</v>
+        <v>0.1175269111990929</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.07893306761980057</v>
+        <v>0.008628770709037781</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.2749474346637726</v>
+        <v>0.1995585560798645</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.06947876513004303</v>
+        <v>0.1935864388942719</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.1030310243368149</v>
+        <v>0.03053360432386398</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.3104412257671356</v>
+        <v>0.1627426445484161</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.1382138133049011</v>
+        <v>0.2902105152606964</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.1710902601480484</v>
+        <v>0.1830323338508606</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.1514442712068558</v>
+        <v>0.1612802296876907</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.1365577876567841</v>
+        <v>0.2081024944782257</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.154307559132576</v>
+        <v>0.03870616853237152</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1827547401189804</v>
+        <v>0.01948732882738113</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.006807371973991394</v>
+        <v>0.3967071175575256</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.04828403517603874</v>
+        <v>0.144148975610733</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.07718504220247269</v>
+        <v>0.1222541630268097</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.1069734692573547</v>
+        <v>0.3370934426784515</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.05345487222075462</v>
+        <v>0.1998439729213715</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.2686589062213898</v>
+        <v>0.08246991038322449</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.03132621571421623</v>
+        <v>0.06257987767457962</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.1046399474143982</v>
+        <v>0.2375799864530563</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.07016362249851227</v>
+        <v>0.3680876195430756</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0588342659175396</v>
+        <v>0.6143237352371216</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.01723785698413849</v>
+        <v>0.2994651794433594</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.09701593965291977</v>
+        <v>0.04778685420751572</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01401578821241856</v>
+        <v>0.4175926744937897</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.06058432534337044</v>
+        <v>0.2781196236610413</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.01227173767983913</v>
+        <v>0.4359074234962463</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.02701780572533607</v>
+        <v>0.4850861430168152</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.2454353868961334</v>
+        <v>0.2713158130645752</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.1534387916326523</v>
+        <v>0.3373424410820007</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.1370709389448166</v>
+        <v>0.7695785760879517</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.09993056952953339</v>
+        <v>0.1202555298805237</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.234009325504303</v>
+        <v>0.6619278192520142</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.3053976893424988</v>
+        <v>0.4138425290584564</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.1054039597511292</v>
+        <v>0.1008172035217285</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.02449970506131649</v>
+        <v>0.3672768473625183</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.005827286280691624</v>
+        <v>0.9430080056190491</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.1003322303295135</v>
+        <v>0.3014031946659088</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02141768299043179</v>
+        <v>0.7141110897064209</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.06822192668914795</v>
+        <v>0.4742826819419861</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.05670862272381783</v>
+        <v>0.02296196669340134</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.1061685085296631</v>
+        <v>0.09068579971790314</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.07953757047653198</v>
+        <v>0.1115282252430916</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.07594138383865356</v>
+        <v>0.3244221210479736</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.130971685051918</v>
+        <v>0.5502086281776428</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.04311869293451309</v>
+        <v>0.2385734170675278</v>
       </c>
     </row>
   </sheetData>
